--- a/grc/sentinel/assets/Sentinel_Defense_GRC_Project_01.xlsx
+++ b/grc/sentinel/assets/Sentinel_Defense_GRC_Project_01.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E396DB4-2D77-4581-BA35-D204867B9535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CEEB61-A417-452A-A56B-6D3AC2F862D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showSheetTabs="0" xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showSheetTabs="0" xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="ControlIDs">'Control Assessment'!$E$7:$E$106</definedName>
     <definedName name="RiskIDs">'Risk Register'!$E$7:$E$106</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="156">
   <si>
     <t>Risk ID</t>
   </si>
@@ -112,12 +112,6 @@
     <t>Missing MFA</t>
   </si>
   <si>
-    <t>Fictional Sentinel Defense Solutions scenario: missing MFA. Supplied scenario values: likelihood 3, impact 4.</t>
-  </si>
-  <si>
-    <t>Affected accounts, applications, exceptions, duration, exploitability and business exposure are unverified.</t>
-  </si>
-  <si>
     <t>Pending scope confirmation</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
   </si>
   <si>
     <t>Proposed</t>
-  </si>
-  <si>
-    <t>Simulated assessment only. Owner and treatment are proposals; residual risk is unassessed. Confirm scope and collect evidence before validating.</t>
   </si>
   <si>
     <t>Control ID</t>
@@ -346,9 +337,6 @@
     <t>Low</t>
   </si>
   <si>
-    <t>R-001 supplied scenario: likelihood 3 × impact 4 = 12 High. These are simulated inputs, not a validated measurement of the organization. Rating boundaries above are proposed methodology assumptions.</t>
-  </si>
-  <si>
     <t>Design effectiveness: the policy and configuration could meet the objective if followed. Operating effectiveness: dated evidence shows the control actually worked over an agreed period. Configuration alone does not establish consistent operation.</t>
   </si>
   <si>
@@ -490,6 +478,39 @@
   <si>
     <t>Use the left sidebar on every page. The current section is highlighted in cyan; Dashboard returns to the overview. Four dedicated columns keep navigation clear of the data. Bottom worksheet tabs remain hidden. Mint dropdowns filter risk views. Native charts include hidden source data and update when inputs change.</t>
   </si>
+  <si>
+    <t>Scoring decision | October 14, 2026: Restored user-defined bands: Low 1–5, Moderate 6–11, High 12–19, Critical 20–25. Supersedes High 10–16 / Critical 17–25. Moderate covers 6–11 so the scale has no gaps. R-001: 3 × 4 = 12 High remains simulated and pending validation.</t>
+  </si>
+  <si>
+    <t>R-002</t>
+  </si>
+  <si>
+    <t>Excessive Access Permissions</t>
+  </si>
+  <si>
+    <t>Sentinel Defense Solutions' fictional case scenario identifies concerns that some employees may have access to files beyond their assigned job responsibilities. Source: Project 01 fictional case study.</t>
+  </si>
+  <si>
+    <t>The number of affected employees, specific file repositories, actual permission assignments, sensitivity of accessible records, effectiveness of existing access controls, and frequency of access reviews have not been verified.</t>
+  </si>
+  <si>
+    <t>Customer records, employee PII, contract documentation</t>
+  </si>
+  <si>
+    <t>IT Security Manager — proposed</t>
+  </si>
+  <si>
+    <t>Sentinel Defense Solutions' fictional case study identifies that some employees do not have multifactor authentication (MFA) enabled. Source: Project 01 fictional case study. The number of affected accounts and whether privileged accounts are included have not been established.</t>
+  </si>
+  <si>
+    <t>The number and roles of accounts without MFA, identity provider configuration, MFA enforcement policies, exceptions, compensating controls, and historical authentication activity have not been verified. No account compromise or data breach has been established.</t>
+  </si>
+  <si>
+    <t>Provisional assessment: Likelihood 3/5 (Possible) and Impact 4/5 (Major), resulting in a High risk score of 12/25. Inconsistent MFA enforcement increases the possibility of unauthorized account access if credentials are compromised. Potential consequences include exposure of sensitive records, operational disruption, and contractual or financial impacts. Recommend enforcing MFA across applicable accounts, prioritizing privileged access, reviewing approved exceptions, and monitoring authentication activity. Validate through identity-provider configurations, account-level MFA coverage reports, exception records, and relevant authentication logs. No compromise or confirmed control failure beyond the stated MFA gap has been established.</t>
+  </si>
+  <si>
+    <t>Provisional assessment: Likelihood 3/5 (Possible) and Impact 4/5 (Major), resulting in a High risk score of 12/25. Suspected excessive permissions could allow employees or compromised accounts to access, modify, or disclose sensitive information beyond legitimate business requirements. Recommend validating current permissions against documented job responsibilities, removing unjustified access, enforcing least privilege, and establishing periodic access reviews. Request permission exports, role definitions, access approvals, group memberships, and prior review records. The extent of excessive access, effectiveness of existing controls, and any actual unauthorized disclosure remain unverified.</t>
+  </si>
 </sst>
 </file>
 
@@ -498,7 +519,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -614,6 +635,10 @@
       <color rgb="FFA5BDD1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="13">
@@ -772,7 +797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -826,10 +851,55 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -850,26 +920,11 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -877,7 +932,10 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -898,39 +956,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1443,7 +1469,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2662,7 +2688,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="1657350"/>
+          <a:off x="133350" y="1642341"/>
           <a:ext cx="1866900" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -2701,7 +2727,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>330835</xdr:rowOff>
+      <xdr:rowOff>304819</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1866900" cy="457200"/>
     <xdr:sp macro="" textlink="">
@@ -2720,7 +2746,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="2286000"/>
+          <a:off x="133350" y="2238683"/>
           <a:ext cx="1866900" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -2759,7 +2785,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>959485</xdr:rowOff>
+      <xdr:rowOff>901161</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1866900" cy="457200"/>
     <xdr:sp macro="" textlink="">
@@ -2778,7 +2804,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="2914650"/>
+          <a:off x="133350" y="2835025"/>
           <a:ext cx="1866900" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -2816,8 +2842,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>90170</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1497503</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1866900" cy="457200"/>
     <xdr:sp macro="" textlink="">
@@ -2836,7 +2862,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="3543300"/>
+          <a:off x="133350" y="3431367"/>
           <a:ext cx="1866900" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -2873,9 +2899,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>55880</xdr:rowOff>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>2093845</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1866900" cy="457200"/>
     <xdr:sp macro="" textlink="">
@@ -2894,7 +2920,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="4171950"/>
+          <a:off x="158750" y="4027709"/>
           <a:ext cx="1866900" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -2931,9 +2957,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>21590</xdr:rowOff>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>2690187</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1866900" cy="457200"/>
     <xdr:sp macro="" textlink="">
@@ -2952,7 +2978,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="4800600"/>
+          <a:off x="158750" y="4624051"/>
           <a:ext cx="1866900" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -2989,9 +3015,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>318770</xdr:rowOff>
+      <xdr:colOff>128155</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>82665</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1866900" cy="457200"/>
     <xdr:sp macro="" textlink="">
@@ -3010,7 +3036,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="133350" y="5429250"/>
+          <a:off x="128155" y="5220392"/>
           <a:ext cx="1866900" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -6785,10 +6811,10 @@
       <c r="AA2" s="13"/>
       <c r="AB2" s="13"/>
       <c r="AE2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AF2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="15" customHeight="1">
@@ -6821,9 +6847,9 @@
       <c r="AA3" s="12"/>
       <c r="AB3" s="12"/>
       <c r="AE3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF3" t="n">
+        <v>97</v>
+      </c>
+      <c r="AF3">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$N$7:$N$106,AE3)</f>
         <v>0</v>
       </c>
@@ -6858,9 +6884,9 @@
       <c r="AA4" s="12"/>
       <c r="AB4" s="12"/>
       <c r="AE4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF4" t="n">
+        <v>84</v>
+      </c>
+      <c r="AF4">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$N$7:$N$106,AE4)</f>
         <v>0</v>
       </c>
@@ -6871,37 +6897,37 @@
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="50"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5" s="50"/>
+      <c r="F5" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
       <c r="AE5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF5">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$N$7:$N$106,AE5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="21" customHeight="1">
@@ -6914,33 +6940,33 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
-      <c r="T6" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="49"/>
-      <c r="AB6" s="49"/>
+      <c r="T6" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
       <c r="AE6" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF6" t="n">
+        <v>96</v>
+      </c>
+      <c r="AF6">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$N$7:$N$106,AE6)</f>
         <v>0</v>
       </c>
@@ -6957,24 +6983,24 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
-      <c r="L7" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
+      <c r="L7" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
-      <c r="T7" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
+      <c r="T7" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="23"/>
+      <c r="Y7" s="23"/>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
@@ -6985,31 +7011,31 @@
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="9"/>
-      <c r="F8" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
+      <c r="F8" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="46"/>
+      <c r="Y8" s="46"/>
+      <c r="Z8" s="46"/>
+      <c r="AA8" s="46"/>
+      <c r="AB8" s="46"/>
     </row>
     <row r="9" spans="1:33" ht="21" customHeight="1">
       <c r="A9" s="18"/>
@@ -7041,10 +7067,10 @@
       <c r="AA9" s="9"/>
       <c r="AB9" s="9"/>
       <c r="AE9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AF9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="21" customHeight="1">
@@ -7053,41 +7079,41 @@
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
       <c r="E10" s="9"/>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="26"/>
+      <c r="AE10" t="s">
         <v>128</v>
       </c>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="45"/>
-      <c r="AE10" t="s">
-        <v>132</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AF10">
         <f>COUNTIFS('Evidence Tracker'!$E$7:$E$106,"&lt;&gt;",'Evidence Tracker'!$N$7:$N$106,"Planned request")</f>
         <v>1</v>
       </c>
@@ -7098,33 +7124,33 @@
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="48"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="29"/>
       <c r="K11" s="9"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="48"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="29"/>
       <c r="Q11" s="9"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="47"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="48"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="29"/>
       <c r="W11" s="9"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="47"/>
-      <c r="AA11" s="47"/>
-      <c r="AB11" s="48"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="28"/>
+      <c r="AA11" s="28"/>
+      <c r="AB11" s="29"/>
       <c r="AE11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AF11" t="n">
+        <v>129</v>
+      </c>
+      <c r="AF11">
         <f>COUNTIFS('Evidence Tracker'!$E$7:$E$106,"&lt;&gt;",'Evidence Tracker'!$N$7:$N$106,"Requested")</f>
         <v>0</v>
       </c>
@@ -7135,45 +7161,45 @@
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="36">
         <f>SUM('Risk Register'!$Y$7:$Y$106)</f>
-        <v>1</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
+        <v>2</v>
+      </c>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38"/>
       <c r="K12" s="9"/>
-      <c r="L12" s="27" t="n">
+      <c r="L12" s="30">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$N$7:$N$106,"High")+COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$N$7:$N$106,"Critical")</f>
-        <v>1</v>
-      </c>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="29"/>
+        <v>2</v>
+      </c>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="32"/>
       <c r="Q12" s="9"/>
-      <c r="R12" s="21" t="n">
+      <c r="R12" s="36">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$Q$7:$Q$106,"Validated")</f>
         <v>0</v>
       </c>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="23"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="38"/>
       <c r="W12" s="9"/>
-      <c r="X12" s="21" t="n">
+      <c r="X12" s="36">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$Q$7:$Q$106,"Pending validation")</f>
-        <v>1</v>
-      </c>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="23"/>
+        <v>2</v>
+      </c>
+      <c r="Y12" s="37"/>
+      <c r="Z12" s="37"/>
+      <c r="AA12" s="37"/>
+      <c r="AB12" s="38"/>
       <c r="AE12" t="s">
-        <v>134</v>
-      </c>
-      <c r="AF12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF12">
         <f>COUNTIFS('Evidence Tracker'!$E$7:$E$106,"&lt;&gt;",'Evidence Tracker'!$N$7:$N$106,"Received")</f>
         <v>0</v>
       </c>
@@ -7184,33 +7210,33 @@
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="26"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="41"/>
       <c r="K13" s="9"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="32"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="35"/>
       <c r="Q13" s="9"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="26"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="41"/>
       <c r="W13" s="9"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="25"/>
-      <c r="Z13" s="25"/>
-      <c r="AA13" s="25"/>
-      <c r="AB13" s="26"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="41"/>
       <c r="AE13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AF13" t="n">
+        <v>131</v>
+      </c>
+      <c r="AF13">
         <f>COUNTIFS('Evidence Tracker'!$E$7:$E$106,"&lt;&gt;",'Evidence Tracker'!$N$7:$N$106,"Under review")</f>
         <v>0</v>
       </c>
@@ -7245,9 +7271,9 @@
       <c r="AA14" s="9"/>
       <c r="AB14" s="9"/>
       <c r="AE14" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF14" t="n">
+        <v>132</v>
+      </c>
+      <c r="AF14">
         <f>COUNTIFS('Evidence Tracker'!$E$7:$E$106,"&lt;&gt;",'Evidence Tracker'!$N$7:$N$106,"Reviewed")</f>
         <v>0</v>
       </c>
@@ -7258,33 +7284,33 @@
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
+      <c r="F15" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
       <c r="Q15" s="9"/>
-      <c r="R15" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
+      <c r="R15" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="S15" s="47"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="47"/>
+      <c r="V15" s="47"/>
+      <c r="W15" s="47"/>
+      <c r="X15" s="47"/>
+      <c r="Y15" s="47"/>
+      <c r="Z15" s="47"/>
+      <c r="AA15" s="47"/>
+      <c r="AB15" s="47"/>
     </row>
     <row r="16" spans="1:33" ht="21" customHeight="1">
       <c r="A16" s="18"/>
@@ -7315,15 +7341,15 @@
       <c r="Z16" s="9"/>
       <c r="AA16" s="9"/>
       <c r="AB16" s="9"/>
-      <c r="AE16" t="n">
+      <c r="AE16">
         <f>'Scoring Methodology'!F16</f>
-        <v>5</v>
-      </c>
-      <c r="AF16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF16">
         <f>'Scoring Methodology'!F17</f>
         <v>12</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG16">
         <f>'Scoring Methodology'!F18</f>
         <v>20</v>
       </c>
@@ -7396,23 +7422,23 @@
       <c r="U18" s="10">
         <v>5</v>
       </c>
-      <c r="V18" s="11" t="n">
+      <c r="V18" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U18,'Risk Register'!$L$7:$L$106,V$17)</f>
         <v>0</v>
       </c>
-      <c r="W18" s="11" t="n">
+      <c r="W18" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U18,'Risk Register'!$L$7:$L$106,W$17)</f>
         <v>0</v>
       </c>
-      <c r="X18" s="11" t="n">
+      <c r="X18" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U18,'Risk Register'!$L$7:$L$106,X$17)</f>
         <v>0</v>
       </c>
-      <c r="Y18" s="11" t="n">
+      <c r="Y18" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U18,'Risk Register'!$L$7:$L$106,Y$17)</f>
         <v>0</v>
       </c>
-      <c r="Z18" s="11" t="n">
+      <c r="Z18" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U18,'Risk Register'!$L$7:$L$106,Z$17)</f>
         <v>0</v>
       </c>
@@ -7443,23 +7469,23 @@
       <c r="U19" s="10">
         <v>4</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U19,'Risk Register'!$L$7:$L$106,V$17)</f>
         <v>0</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U19,'Risk Register'!$L$7:$L$106,W$17)</f>
         <v>0</v>
       </c>
-      <c r="X19" s="11" t="n">
+      <c r="X19" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U19,'Risk Register'!$L$7:$L$106,X$17)</f>
         <v>0</v>
       </c>
-      <c r="Y19" s="11" t="n">
+      <c r="Y19" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U19,'Risk Register'!$L$7:$L$106,Y$17)</f>
         <v>0</v>
       </c>
-      <c r="Z19" s="11" t="n">
+      <c r="Z19" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U19,'Risk Register'!$L$7:$L$106,Z$17)</f>
         <v>0</v>
       </c>
@@ -7490,23 +7516,23 @@
       <c r="U20" s="10">
         <v>3</v>
       </c>
-      <c r="V20" s="11" t="n">
+      <c r="V20" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U20,'Risk Register'!$L$7:$L$106,V$17)</f>
         <v>0</v>
       </c>
-      <c r="W20" s="11" t="n">
+      <c r="W20" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U20,'Risk Register'!$L$7:$L$106,W$17)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="11" t="n">
+      <c r="X20" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U20,'Risk Register'!$L$7:$L$106,X$17)</f>
         <v>0</v>
       </c>
-      <c r="Y20" s="11" t="n">
+      <c r="Y20" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U20,'Risk Register'!$L$7:$L$106,Y$17)</f>
-        <v>1</v>
-      </c>
-      <c r="Z20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U20,'Risk Register'!$L$7:$L$106,Z$17)</f>
         <v>0</v>
       </c>
@@ -7537,23 +7563,23 @@
       <c r="U21" s="10">
         <v>2</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U21,'Risk Register'!$L$7:$L$106,V$17)</f>
         <v>0</v>
       </c>
-      <c r="W21" s="11" t="n">
+      <c r="W21" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U21,'Risk Register'!$L$7:$L$106,W$17)</f>
         <v>0</v>
       </c>
-      <c r="X21" s="11" t="n">
+      <c r="X21" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U21,'Risk Register'!$L$7:$L$106,X$17)</f>
         <v>0</v>
       </c>
-      <c r="Y21" s="11" t="n">
+      <c r="Y21" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U21,'Risk Register'!$L$7:$L$106,Y$17)</f>
         <v>0</v>
       </c>
-      <c r="Z21" s="11" t="n">
+      <c r="Z21" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U21,'Risk Register'!$L$7:$L$106,Z$17)</f>
         <v>0</v>
       </c>
@@ -7584,23 +7610,23 @@
       <c r="U22" s="10">
         <v>1</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U22,'Risk Register'!$L$7:$L$106,V$17)</f>
         <v>0</v>
       </c>
-      <c r="W22" s="11" t="n">
+      <c r="W22" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U22,'Risk Register'!$L$7:$L$106,W$17)</f>
         <v>0</v>
       </c>
-      <c r="X22" s="11" t="n">
+      <c r="X22" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U22,'Risk Register'!$L$7:$L$106,X$17)</f>
         <v>0</v>
       </c>
-      <c r="Y22" s="11" t="n">
+      <c r="Y22" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U22,'Risk Register'!$L$7:$L$106,Y$17)</f>
         <v>0</v>
       </c>
-      <c r="Z22" s="11" t="n">
+      <c r="Z22" s="11">
         <f>COUNTIFS('Risk Register'!$Y$7:$Y$106,1,'Risk Register'!$K$7:$K$106,$U22,'Risk Register'!$L$7:$L$106,Z$17)</f>
         <v>0</v>
       </c>
@@ -7655,19 +7681,19 @@
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
-      <c r="R24" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
+      <c r="R24" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="46"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="46"/>
+      <c r="AA24" s="46"/>
+      <c r="AB24" s="46"/>
     </row>
     <row r="25" spans="1:31" ht="21" customHeight="1">
       <c r="A25" s="18"/>
@@ -7687,17 +7713,17 @@
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="46"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="46"/>
+      <c r="AB25" s="46"/>
     </row>
     <row r="26" spans="1:31" ht="21" customHeight="1">
       <c r="A26" s="18"/>
@@ -7765,20 +7791,20 @@
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="19" t="str">
+      <c r="F28" s="46" t="str">
         <f>IF(F12=0,"No risks match these filters.","Risk distribution total: "&amp;SUM(AF3:AF6)&amp;" / "&amp;F12&amp;" risks in view")</f>
-        <v>Risk distribution total: 1 / 1 risks in view</v>
-      </c>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
+        <v>Risk distribution total: 2 / 2 risks in view</v>
+      </c>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
@@ -7828,33 +7854,33 @@
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
       <c r="E30" s="9"/>
-      <c r="F30" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
+      <c r="F30" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="47"/>
+      <c r="N30" s="47"/>
+      <c r="O30" s="47"/>
+      <c r="P30" s="47"/>
       <c r="Q30" s="9"/>
-      <c r="R30" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="S30" s="33"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="33"/>
-      <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="33"/>
-      <c r="Y30" s="33"/>
-      <c r="Z30" s="33"/>
-      <c r="AA30" s="33"/>
-      <c r="AB30" s="33"/>
+      <c r="R30" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="S30" s="47"/>
+      <c r="T30" s="47"/>
+      <c r="U30" s="47"/>
+      <c r="V30" s="47"/>
+      <c r="W30" s="47"/>
+      <c r="X30" s="47"/>
+      <c r="Y30" s="47"/>
+      <c r="Z30" s="47"/>
+      <c r="AA30" s="47"/>
+      <c r="AB30" s="47"/>
     </row>
     <row r="31" spans="1:31" ht="21" customHeight="1">
       <c r="A31" s="18"/>
@@ -7904,22 +7930,22 @@
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
-      <c r="R32" s="34" t="s">
+      <c r="R32" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="34"/>
-      <c r="W32" s="34"/>
-      <c r="X32" s="34"/>
-      <c r="Y32" s="35" t="str">
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
+      <c r="U32" s="44"/>
+      <c r="V32" s="44"/>
+      <c r="W32" s="44"/>
+      <c r="X32" s="44"/>
+      <c r="Y32" s="45" t="str">
         <f>'Risk Register'!M7&amp;" / "&amp;'Risk Register'!N7</f>
         <v>12 / High</v>
       </c>
-      <c r="Z32" s="35"/>
-      <c r="AA32" s="35"/>
-      <c r="AB32" s="35"/>
+      <c r="Z32" s="45"/>
+      <c r="AA32" s="45"/>
+      <c r="AB32" s="45"/>
     </row>
     <row r="33" spans="1:28" ht="21" customHeight="1">
       <c r="A33" s="18"/>
@@ -7939,17 +7965,17 @@
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Y33" s="35"/>
-      <c r="Z33" s="35"/>
-      <c r="AA33" s="35"/>
-      <c r="AB33" s="35"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
+      <c r="U33" s="44"/>
+      <c r="V33" s="44"/>
+      <c r="W33" s="44"/>
+      <c r="X33" s="44"/>
+      <c r="Y33" s="45"/>
+      <c r="Z33" s="45"/>
+      <c r="AA33" s="45"/>
+      <c r="AB33" s="45"/>
     </row>
     <row r="34" spans="1:28" ht="21" customHeight="1">
       <c r="A34" s="18"/>
@@ -7999,19 +8025,19 @@
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
-      <c r="R35" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="36"/>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="36"/>
-      <c r="Y35" s="36"/>
-      <c r="Z35" s="36"/>
-      <c r="AA35" s="36"/>
-      <c r="AB35" s="36"/>
+      <c r="R35" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="S35" s="42"/>
+      <c r="T35" s="42"/>
+      <c r="U35" s="42"/>
+      <c r="V35" s="42"/>
+      <c r="W35" s="42"/>
+      <c r="X35" s="42"/>
+      <c r="Y35" s="42"/>
+      <c r="Z35" s="42"/>
+      <c r="AA35" s="42"/>
+      <c r="AB35" s="42"/>
     </row>
     <row r="36" spans="1:28" ht="21" customHeight="1">
       <c r="A36" s="18"/>
@@ -8031,17 +8057,17 @@
       <c r="O36" s="9"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
-      <c r="R36" s="36"/>
-      <c r="S36" s="36"/>
-      <c r="T36" s="36"/>
-      <c r="U36" s="36"/>
-      <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="36"/>
-      <c r="Z36" s="36"/>
-      <c r="AA36" s="36"/>
-      <c r="AB36" s="36"/>
+      <c r="R36" s="42"/>
+      <c r="S36" s="42"/>
+      <c r="T36" s="42"/>
+      <c r="U36" s="42"/>
+      <c r="V36" s="42"/>
+      <c r="W36" s="42"/>
+      <c r="X36" s="42"/>
+      <c r="Y36" s="42"/>
+      <c r="Z36" s="42"/>
+      <c r="AA36" s="42"/>
+      <c r="AB36" s="42"/>
     </row>
     <row r="37" spans="1:28" ht="21" customHeight="1">
       <c r="A37" s="18"/>
@@ -8061,17 +8087,17 @@
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
-      <c r="R37" s="36"/>
-      <c r="S37" s="36"/>
-      <c r="T37" s="36"/>
-      <c r="U37" s="36"/>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="36"/>
-      <c r="Y37" s="36"/>
-      <c r="Z37" s="36"/>
-      <c r="AA37" s="36"/>
-      <c r="AB37" s="36"/>
+      <c r="R37" s="42"/>
+      <c r="S37" s="42"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="42"/>
+      <c r="V37" s="42"/>
+      <c r="W37" s="42"/>
+      <c r="X37" s="42"/>
+      <c r="Y37" s="42"/>
+      <c r="Z37" s="42"/>
+      <c r="AA37" s="42"/>
+      <c r="AB37" s="42"/>
     </row>
     <row r="38" spans="1:28" ht="21" customHeight="1">
       <c r="A38" s="18"/>
@@ -8121,19 +8147,19 @@
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
-      <c r="R39" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="S39" s="19"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="19"/>
-      <c r="W39" s="19"/>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="19"/>
-      <c r="Z39" s="19"/>
+      <c r="R39" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="S39" s="46"/>
+      <c r="T39" s="46"/>
+      <c r="U39" s="46"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="46"/>
+      <c r="Z39" s="46"/>
       <c r="AA39" s="9"/>
-      <c r="AB39" s="9" t="n">
+      <c r="AB39" s="9">
         <f>COUNTIFS('Evidence Tracker'!$E$7:$E$106,"&lt;&gt;",'Evidence Tracker'!$Q$7:$Q$106,"Validated")</f>
         <v>0</v>
       </c>
@@ -8156,19 +8182,19 @@
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
-      <c r="R40" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="19"/>
-      <c r="X40" s="19"/>
-      <c r="Y40" s="19"/>
-      <c r="Z40" s="19"/>
+      <c r="R40" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="S40" s="46"/>
+      <c r="T40" s="46"/>
+      <c r="U40" s="46"/>
+      <c r="V40" s="46"/>
+      <c r="W40" s="46"/>
+      <c r="X40" s="46"/>
+      <c r="Y40" s="46"/>
+      <c r="Z40" s="46"/>
       <c r="AA40" s="9"/>
-      <c r="AB40" s="9" t="n">
+      <c r="AB40" s="9">
         <f ca="1">COUNTIFS('Remediation Tracker'!$O$7:$O$106,"&gt;0")</f>
         <v>0</v>
       </c>
@@ -8239,31 +8265,31 @@
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
       <c r="E43" s="9"/>
-      <c r="F43" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="36"/>
-      <c r="O43" s="36"/>
-      <c r="P43" s="36"/>
-      <c r="Q43" s="36"/>
-      <c r="R43" s="36"/>
-      <c r="S43" s="36"/>
-      <c r="T43" s="36"/>
-      <c r="U43" s="36"/>
-      <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
-      <c r="X43" s="36"/>
-      <c r="Y43" s="36"/>
-      <c r="Z43" s="36"/>
-      <c r="AA43" s="36"/>
-      <c r="AB43" s="36"/>
+      <c r="F43" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="42"/>
+      <c r="O43" s="42"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="42"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="42"/>
+      <c r="V43" s="42"/>
+      <c r="W43" s="42"/>
+      <c r="X43" s="42"/>
+      <c r="Y43" s="42"/>
+      <c r="Z43" s="42"/>
+      <c r="AA43" s="42"/>
+      <c r="AB43" s="42"/>
     </row>
     <row r="44" spans="1:28" ht="21" customHeight="1">
       <c r="A44" s="18"/>
@@ -8271,29 +8297,29 @@
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
       <c r="E44" s="9"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="36"/>
-      <c r="O44" s="36"/>
-      <c r="P44" s="36"/>
-      <c r="Q44" s="36"/>
-      <c r="R44" s="36"/>
-      <c r="S44" s="36"/>
-      <c r="T44" s="36"/>
-      <c r="U44" s="36"/>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="36"/>
-      <c r="Y44" s="36"/>
-      <c r="Z44" s="36"/>
-      <c r="AA44" s="36"/>
-      <c r="AB44" s="36"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="42"/>
+      <c r="N44" s="42"/>
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="42"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="42"/>
+      <c r="W44" s="42"/>
+      <c r="X44" s="42"/>
+      <c r="Y44" s="42"/>
+      <c r="Z44" s="42"/>
+      <c r="AA44" s="42"/>
+      <c r="AB44" s="42"/>
     </row>
     <row r="45" spans="1:28" ht="24.95" customHeight="1"/>
     <row r="46" spans="1:28" ht="24.95" customHeight="1"/>
@@ -8333,7 +8359,6 @@
     <mergeCell ref="F8:AB8"/>
     <mergeCell ref="F10:J11"/>
     <mergeCell ref="F12:J13"/>
-    <mergeCell ref="L10:P11"/>
     <mergeCell ref="L12:P13"/>
     <mergeCell ref="R10:V11"/>
     <mergeCell ref="R12:V13"/>
@@ -8343,6 +8368,7 @@
     <mergeCell ref="L7:Q7"/>
     <mergeCell ref="T6:AB6"/>
     <mergeCell ref="T7:Y7"/>
+    <mergeCell ref="L10:P11"/>
   </mergeCells>
   <conditionalFormatting sqref="V18:Z22">
     <cfRule type="expression" dxfId="39" priority="101">
@@ -8536,35 +8562,35 @@
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="19"/>
+      <c r="E5" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
     </row>
     <row r="6" spans="1:25" ht="45.95" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="2" t="s">
         <v>0</v>
       </c>
@@ -8629,11 +8655,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="117.95" customHeight="1">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+    <row r="7" spans="1:25" ht="252" customHeight="1">
+      <c r="A7" s="54"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
@@ -8641,16 +8667,16 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="K7" s="3">
         <v>3</v>
@@ -8658,7 +8684,7 @@
       <c r="L7" s="3">
         <v>4</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="4">
         <f t="shared" ref="M7:M38" si="0">IF(E7="","",IF(OR(K7="",L7=""),"",IF(AND(ISNUMBER(K7),ISNUMBER(L7),K7&gt;=1,K7&lt;=5,L7&gt;=1,L7&lt;=5,MOD(K7,1)=0,MOD(L7,1)=0),K7*L7,"Invalid input")))</f>
         <v>12</v>
       </c>
@@ -8667,81 +8693,109 @@
         <v>High</v>
       </c>
       <c r="O7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="R7" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="4" t="str">
         <f t="shared" ref="V7:V38" si="1">IF(E7="","",IF(OR(T7="",U7=""),"",IF(AND(ISNUMBER(T7),ISNUMBER(U7),T7&gt;=1,T7&lt;=5,U7&gt;=1,U7&lt;=5,MOD(T7,1)=0,MOD(U7,1)=0),T7*U7,"Invalid input")))</f>
+        <v/>
       </c>
       <c r="W7" s="4" t="str">
         <f>IF(V7="","",IF(ISNUMBER(V7),IF(V7&lt;'Scoring Methodology'!$F$16,"Low",IF(V7&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V7&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y7" s="4" t="n">
+        <v>154</v>
+      </c>
+      <c r="Y7" s="4">
         <f>IF(E7="",0,IF(AND(OR(Dashboard!$L$7="All",Q7=Dashboard!$L$7),OR(Dashboard!$T$7="All",N7=Dashboard!$T$7)),1,0))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="4" t="n">
+    <row r="8" spans="1:25" ht="229.5" customHeight="1">
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
+        <v>4</v>
+      </c>
+      <c r="M8" s="4">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="N8" s="4" t="str">
         <f>IF(M8="","",IF(ISNUMBER(M8),IF(M8&lt;'Scoring Methodology'!$F$16,"Low",IF(M8&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M8&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+        <v>High</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="4" t="n">
+      <c r="V8" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v/>
       </c>
       <c r="W8" s="4" t="str">
         <f>IF(V8="","",IF(ISNUMBER(V8),IF(V8&lt;'Scoring Methodology'!$F$16,"Low",IF(V8&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V8&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="4" t="n">
+        <v/>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y8" s="4">
         <f>IF(E8="",0,IF(AND(OR(Dashboard!$L$7="All",Q8=Dashboard!$L$7),OR(Dashboard!$T$7="All",N8=Dashboard!$T$7)),1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -8752,9 +8806,11 @@
       <c r="L9" s="3"/>
       <c r="M9" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N9" s="4" t="str">
         <f>IF(M9="","",IF(ISNUMBER(M9),IF(M9&lt;'Scoring Methodology'!$F$16,"Low",IF(M9&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M9&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -8765,21 +8821,23 @@
       <c r="U9" s="3"/>
       <c r="V9" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W9" s="4" t="str">
         <f>IF(V9="","",IF(ISNUMBER(V9),IF(V9&lt;'Scoring Methodology'!$F$16,"Low",IF(V9&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V9&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X9" s="3"/>
-      <c r="Y9" s="4" t="n">
+      <c r="Y9" s="4">
         <f>IF(E9="",0,IF(AND(OR(Dashboard!$L$7="All",Q9=Dashboard!$L$7),OR(Dashboard!$T$7="All",N9=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -8790,9 +8848,11 @@
       <c r="L10" s="3"/>
       <c r="M10" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N10" s="4" t="str">
         <f>IF(M10="","",IF(ISNUMBER(M10),IF(M10&lt;'Scoring Methodology'!$F$16,"Low",IF(M10&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M10&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -8803,21 +8863,23 @@
       <c r="U10" s="3"/>
       <c r="V10" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W10" s="4" t="str">
         <f>IF(V10="","",IF(ISNUMBER(V10),IF(V10&lt;'Scoring Methodology'!$F$16,"Low",IF(V10&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V10&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X10" s="3"/>
-      <c r="Y10" s="4" t="n">
+      <c r="Y10" s="4">
         <f>IF(E10="",0,IF(AND(OR(Dashboard!$L$7="All",Q10=Dashboard!$L$7),OR(Dashboard!$T$7="All",N10=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -8828,9 +8890,11 @@
       <c r="L11" s="3"/>
       <c r="M11" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N11" s="4" t="str">
         <f>IF(M11="","",IF(ISNUMBER(M11),IF(M11&lt;'Scoring Methodology'!$F$16,"Low",IF(M11&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M11&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -8841,21 +8905,23 @@
       <c r="U11" s="3"/>
       <c r="V11" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W11" s="4" t="str">
         <f>IF(V11="","",IF(ISNUMBER(V11),IF(V11&lt;'Scoring Methodology'!$F$16,"Low",IF(V11&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V11&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X11" s="3"/>
-      <c r="Y11" s="4" t="n">
+      <c r="Y11" s="4">
         <f>IF(E11="",0,IF(AND(OR(Dashboard!$L$7="All",Q11=Dashboard!$L$7),OR(Dashboard!$T$7="All",N11=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -8866,9 +8932,11 @@
       <c r="L12" s="3"/>
       <c r="M12" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N12" s="4" t="str">
         <f>IF(M12="","",IF(ISNUMBER(M12),IF(M12&lt;'Scoring Methodology'!$F$16,"Low",IF(M12&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M12&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -8879,21 +8947,23 @@
       <c r="U12" s="3"/>
       <c r="V12" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W12" s="4" t="str">
         <f>IF(V12="","",IF(ISNUMBER(V12),IF(V12&lt;'Scoring Methodology'!$F$16,"Low",IF(V12&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V12&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X12" s="3"/>
-      <c r="Y12" s="4" t="n">
+      <c r="Y12" s="4">
         <f>IF(E12="",0,IF(AND(OR(Dashboard!$L$7="All",Q12=Dashboard!$L$7),OR(Dashboard!$T$7="All",N12=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -8904,9 +8974,11 @@
       <c r="L13" s="3"/>
       <c r="M13" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N13" s="4" t="str">
         <f>IF(M13="","",IF(ISNUMBER(M13),IF(M13&lt;'Scoring Methodology'!$F$16,"Low",IF(M13&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M13&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -8917,21 +8989,23 @@
       <c r="U13" s="3"/>
       <c r="V13" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W13" s="4" t="str">
         <f>IF(V13="","",IF(ISNUMBER(V13),IF(V13&lt;'Scoring Methodology'!$F$16,"Low",IF(V13&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V13&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X13" s="3"/>
-      <c r="Y13" s="4" t="n">
+      <c r="Y13" s="4">
         <f>IF(E13="",0,IF(AND(OR(Dashboard!$L$7="All",Q13=Dashboard!$L$7),OR(Dashboard!$T$7="All",N13=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -8942,9 +9016,11 @@
       <c r="L14" s="3"/>
       <c r="M14" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N14" s="4" t="str">
         <f>IF(M14="","",IF(ISNUMBER(M14),IF(M14&lt;'Scoring Methodology'!$F$16,"Low",IF(M14&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M14&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -8955,21 +9031,23 @@
       <c r="U14" s="3"/>
       <c r="V14" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W14" s="4" t="str">
         <f>IF(V14="","",IF(ISNUMBER(V14),IF(V14&lt;'Scoring Methodology'!$F$16,"Low",IF(V14&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V14&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X14" s="3"/>
-      <c r="Y14" s="4" t="n">
+      <c r="Y14" s="4">
         <f>IF(E14="",0,IF(AND(OR(Dashboard!$L$7="All",Q14=Dashboard!$L$7),OR(Dashboard!$T$7="All",N14=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
+      <c r="A15" s="54"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -8980,9 +9058,11 @@
       <c r="L15" s="3"/>
       <c r="M15" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N15" s="4" t="str">
         <f>IF(M15="","",IF(ISNUMBER(M15),IF(M15&lt;'Scoring Methodology'!$F$16,"Low",IF(M15&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M15&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -8993,21 +9073,23 @@
       <c r="U15" s="3"/>
       <c r="V15" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W15" s="4" t="str">
         <f>IF(V15="","",IF(ISNUMBER(V15),IF(V15&lt;'Scoring Methodology'!$F$16,"Low",IF(V15&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V15&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X15" s="3"/>
-      <c r="Y15" s="4" t="n">
+      <c r="Y15" s="4">
         <f>IF(E15="",0,IF(AND(OR(Dashboard!$L$7="All",Q15=Dashboard!$L$7),OR(Dashboard!$T$7="All",N15=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
+      <c r="A16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -9018,9 +9100,11 @@
       <c r="L16" s="3"/>
       <c r="M16" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N16" s="4" t="str">
         <f>IF(M16="","",IF(ISNUMBER(M16),IF(M16&lt;'Scoring Methodology'!$F$16,"Low",IF(M16&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M16&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -9031,21 +9115,23 @@
       <c r="U16" s="3"/>
       <c r="V16" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W16" s="4" t="str">
         <f>IF(V16="","",IF(ISNUMBER(V16),IF(V16&lt;'Scoring Methodology'!$F$16,"Low",IF(V16&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V16&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X16" s="3"/>
-      <c r="Y16" s="4" t="n">
+      <c r="Y16" s="4">
         <f>IF(E16="",0,IF(AND(OR(Dashboard!$L$7="All",Q16=Dashboard!$L$7),OR(Dashboard!$T$7="All",N16=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -9056,9 +9142,11 @@
       <c r="L17" s="3"/>
       <c r="M17" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N17" s="4" t="str">
         <f>IF(M17="","",IF(ISNUMBER(M17),IF(M17&lt;'Scoring Methodology'!$F$16,"Low",IF(M17&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M17&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -9069,21 +9157,23 @@
       <c r="U17" s="3"/>
       <c r="V17" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W17" s="4" t="str">
         <f>IF(V17="","",IF(ISNUMBER(V17),IF(V17&lt;'Scoring Methodology'!$F$16,"Low",IF(V17&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V17&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X17" s="3"/>
-      <c r="Y17" s="4" t="n">
+      <c r="Y17" s="4">
         <f>IF(E17="",0,IF(AND(OR(Dashboard!$L$7="All",Q17=Dashboard!$L$7),OR(Dashboard!$T$7="All",N17=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
+      <c r="A18" s="54"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -9094,9 +9184,11 @@
       <c r="L18" s="3"/>
       <c r="M18" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N18" s="4" t="str">
         <f>IF(M18="","",IF(ISNUMBER(M18),IF(M18&lt;'Scoring Methodology'!$F$16,"Low",IF(M18&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M18&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -9107,21 +9199,23 @@
       <c r="U18" s="3"/>
       <c r="V18" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W18" s="4" t="str">
         <f>IF(V18="","",IF(ISNUMBER(V18),IF(V18&lt;'Scoring Methodology'!$F$16,"Low",IF(V18&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V18&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X18" s="3"/>
-      <c r="Y18" s="4" t="n">
+      <c r="Y18" s="4">
         <f>IF(E18="",0,IF(AND(OR(Dashboard!$L$7="All",Q18=Dashboard!$L$7),OR(Dashboard!$T$7="All",N18=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -9132,9 +9226,11 @@
       <c r="L19" s="3"/>
       <c r="M19" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N19" s="4" t="str">
         <f>IF(M19="","",IF(ISNUMBER(M19),IF(M19&lt;'Scoring Methodology'!$F$16,"Low",IF(M19&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M19&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -9145,21 +9241,23 @@
       <c r="U19" s="3"/>
       <c r="V19" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W19" s="4" t="str">
         <f>IF(V19="","",IF(ISNUMBER(V19),IF(V19&lt;'Scoring Methodology'!$F$16,"Low",IF(V19&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V19&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X19" s="3"/>
-      <c r="Y19" s="4" t="n">
+      <c r="Y19" s="4">
         <f>IF(E19="",0,IF(AND(OR(Dashboard!$L$7="All",Q19=Dashboard!$L$7),OR(Dashboard!$T$7="All",N19=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -9170,9 +9268,11 @@
       <c r="L20" s="3"/>
       <c r="M20" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N20" s="4" t="str">
         <f>IF(M20="","",IF(ISNUMBER(M20),IF(M20&lt;'Scoring Methodology'!$F$16,"Low",IF(M20&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M20&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -9183,21 +9283,23 @@
       <c r="U20" s="3"/>
       <c r="V20" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W20" s="4" t="str">
         <f>IF(V20="","",IF(ISNUMBER(V20),IF(V20&lt;'Scoring Methodology'!$F$16,"Low",IF(V20&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V20&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X20" s="3"/>
-      <c r="Y20" s="4" t="n">
+      <c r="Y20" s="4">
         <f>IF(E20="",0,IF(AND(OR(Dashboard!$L$7="All",Q20=Dashboard!$L$7),OR(Dashboard!$T$7="All",N20=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -9208,9 +9310,11 @@
       <c r="L21" s="3"/>
       <c r="M21" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N21" s="4" t="str">
         <f>IF(M21="","",IF(ISNUMBER(M21),IF(M21&lt;'Scoring Methodology'!$F$16,"Low",IF(M21&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M21&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -9221,21 +9325,23 @@
       <c r="U21" s="3"/>
       <c r="V21" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W21" s="4" t="str">
         <f>IF(V21="","",IF(ISNUMBER(V21),IF(V21&lt;'Scoring Methodology'!$F$16,"Low",IF(V21&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V21&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X21" s="3"/>
-      <c r="Y21" s="4" t="n">
+      <c r="Y21" s="4">
         <f>IF(E21="",0,IF(AND(OR(Dashboard!$L$7="All",Q21=Dashboard!$L$7),OR(Dashboard!$T$7="All",N21=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -9246,9 +9352,11 @@
       <c r="L22" s="3"/>
       <c r="M22" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N22" s="4" t="str">
         <f>IF(M22="","",IF(ISNUMBER(M22),IF(M22&lt;'Scoring Methodology'!$F$16,"Low",IF(M22&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M22&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -9259,21 +9367,23 @@
       <c r="U22" s="3"/>
       <c r="V22" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W22" s="4" t="str">
         <f>IF(V22="","",IF(ISNUMBER(V22),IF(V22&lt;'Scoring Methodology'!$F$16,"Low",IF(V22&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V22&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X22" s="3"/>
-      <c r="Y22" s="4" t="n">
+      <c r="Y22" s="4">
         <f>IF(E22="",0,IF(AND(OR(Dashboard!$L$7="All",Q22=Dashboard!$L$7),OR(Dashboard!$T$7="All",N22=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -9284,9 +9394,11 @@
       <c r="L23" s="3"/>
       <c r="M23" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N23" s="4" t="str">
         <f>IF(M23="","",IF(ISNUMBER(M23),IF(M23&lt;'Scoring Methodology'!$F$16,"Low",IF(M23&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M23&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -9297,21 +9409,23 @@
       <c r="U23" s="3"/>
       <c r="V23" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W23" s="4" t="str">
         <f>IF(V23="","",IF(ISNUMBER(V23),IF(V23&lt;'Scoring Methodology'!$F$16,"Low",IF(V23&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V23&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X23" s="3"/>
-      <c r="Y23" s="4" t="n">
+      <c r="Y23" s="4">
         <f>IF(E23="",0,IF(AND(OR(Dashboard!$L$7="All",Q23=Dashboard!$L$7),OR(Dashboard!$T$7="All",N23=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -9322,9 +9436,11 @@
       <c r="L24" s="3"/>
       <c r="M24" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N24" s="4" t="str">
         <f>IF(M24="","",IF(ISNUMBER(M24),IF(M24&lt;'Scoring Methodology'!$F$16,"Low",IF(M24&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M24&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -9335,21 +9451,23 @@
       <c r="U24" s="3"/>
       <c r="V24" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W24" s="4" t="str">
         <f>IF(V24="","",IF(ISNUMBER(V24),IF(V24&lt;'Scoring Methodology'!$F$16,"Low",IF(V24&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V24&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X24" s="3"/>
-      <c r="Y24" s="4" t="n">
+      <c r="Y24" s="4">
         <f>IF(E24="",0,IF(AND(OR(Dashboard!$L$7="All",Q24=Dashboard!$L$7),OR(Dashboard!$T$7="All",N24=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -9360,9 +9478,11 @@
       <c r="L25" s="3"/>
       <c r="M25" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N25" s="4" t="str">
         <f>IF(M25="","",IF(ISNUMBER(M25),IF(M25&lt;'Scoring Methodology'!$F$16,"Low",IF(M25&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M25&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -9373,21 +9493,23 @@
       <c r="U25" s="3"/>
       <c r="V25" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W25" s="4" t="str">
         <f>IF(V25="","",IF(ISNUMBER(V25),IF(V25&lt;'Scoring Methodology'!$F$16,"Low",IF(V25&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V25&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X25" s="3"/>
-      <c r="Y25" s="4" t="n">
+      <c r="Y25" s="4">
         <f>IF(E25="",0,IF(AND(OR(Dashboard!$L$7="All",Q25=Dashboard!$L$7),OR(Dashboard!$T$7="All",N25=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -9398,9 +9520,11 @@
       <c r="L26" s="3"/>
       <c r="M26" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N26" s="4" t="str">
         <f>IF(M26="","",IF(ISNUMBER(M26),IF(M26&lt;'Scoring Methodology'!$F$16,"Low",IF(M26&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M26&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -9411,21 +9535,23 @@
       <c r="U26" s="3"/>
       <c r="V26" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W26" s="4" t="str">
         <f>IF(V26="","",IF(ISNUMBER(V26),IF(V26&lt;'Scoring Methodology'!$F$16,"Low",IF(V26&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V26&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X26" s="3"/>
-      <c r="Y26" s="4" t="n">
+      <c r="Y26" s="4">
         <f>IF(E26="",0,IF(AND(OR(Dashboard!$L$7="All",Q26=Dashboard!$L$7),OR(Dashboard!$T$7="All",N26=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
+      <c r="A27" s="54"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -9436,9 +9562,11 @@
       <c r="L27" s="3"/>
       <c r="M27" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N27" s="4" t="str">
         <f>IF(M27="","",IF(ISNUMBER(M27),IF(M27&lt;'Scoring Methodology'!$F$16,"Low",IF(M27&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M27&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -9449,21 +9577,23 @@
       <c r="U27" s="3"/>
       <c r="V27" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W27" s="4" t="str">
         <f>IF(V27="","",IF(ISNUMBER(V27),IF(V27&lt;'Scoring Methodology'!$F$16,"Low",IF(V27&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V27&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X27" s="3"/>
-      <c r="Y27" s="4" t="n">
+      <c r="Y27" s="4">
         <f>IF(E27="",0,IF(AND(OR(Dashboard!$L$7="All",Q27=Dashboard!$L$7),OR(Dashboard!$T$7="All",N27=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -9474,9 +9604,11 @@
       <c r="L28" s="3"/>
       <c r="M28" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N28" s="4" t="str">
         <f>IF(M28="","",IF(ISNUMBER(M28),IF(M28&lt;'Scoring Methodology'!$F$16,"Low",IF(M28&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M28&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -9487,21 +9619,23 @@
       <c r="U28" s="3"/>
       <c r="V28" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W28" s="4" t="str">
         <f>IF(V28="","",IF(ISNUMBER(V28),IF(V28&lt;'Scoring Methodology'!$F$16,"Low",IF(V28&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V28&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X28" s="3"/>
-      <c r="Y28" s="4" t="n">
+      <c r="Y28" s="4">
         <f>IF(E28="",0,IF(AND(OR(Dashboard!$L$7="All",Q28=Dashboard!$L$7),OR(Dashboard!$T$7="All",N28=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
+      <c r="A29" s="54"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -9512,9 +9646,11 @@
       <c r="L29" s="3"/>
       <c r="M29" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N29" s="4" t="str">
         <f>IF(M29="","",IF(ISNUMBER(M29),IF(M29&lt;'Scoring Methodology'!$F$16,"Low",IF(M29&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M29&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -9525,21 +9661,23 @@
       <c r="U29" s="3"/>
       <c r="V29" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W29" s="4" t="str">
         <f>IF(V29="","",IF(ISNUMBER(V29),IF(V29&lt;'Scoring Methodology'!$F$16,"Low",IF(V29&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V29&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X29" s="3"/>
-      <c r="Y29" s="4" t="n">
+      <c r="Y29" s="4">
         <f>IF(E29="",0,IF(AND(OR(Dashboard!$L$7="All",Q29=Dashboard!$L$7),OR(Dashboard!$T$7="All",N29=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -9550,9 +9688,11 @@
       <c r="L30" s="3"/>
       <c r="M30" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N30" s="4" t="str">
         <f>IF(M30="","",IF(ISNUMBER(M30),IF(M30&lt;'Scoring Methodology'!$F$16,"Low",IF(M30&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M30&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -9563,21 +9703,23 @@
       <c r="U30" s="3"/>
       <c r="V30" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W30" s="4" t="str">
         <f>IF(V30="","",IF(ISNUMBER(V30),IF(V30&lt;'Scoring Methodology'!$F$16,"Low",IF(V30&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V30&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X30" s="3"/>
-      <c r="Y30" s="4" t="n">
+      <c r="Y30" s="4">
         <f>IF(E30="",0,IF(AND(OR(Dashboard!$L$7="All",Q30=Dashboard!$L$7),OR(Dashboard!$T$7="All",N30=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -9588,9 +9730,11 @@
       <c r="L31" s="3"/>
       <c r="M31" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N31" s="4" t="str">
         <f>IF(M31="","",IF(ISNUMBER(M31),IF(M31&lt;'Scoring Methodology'!$F$16,"Low",IF(M31&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M31&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -9601,21 +9745,23 @@
       <c r="U31" s="3"/>
       <c r="V31" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W31" s="4" t="str">
         <f>IF(V31="","",IF(ISNUMBER(V31),IF(V31&lt;'Scoring Methodology'!$F$16,"Low",IF(V31&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V31&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X31" s="3"/>
-      <c r="Y31" s="4" t="n">
+      <c r="Y31" s="4">
         <f>IF(E31="",0,IF(AND(OR(Dashboard!$L$7="All",Q31=Dashboard!$L$7),OR(Dashboard!$T$7="All",N31=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
+      <c r="A32" s="54"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -9626,9 +9772,11 @@
       <c r="L32" s="3"/>
       <c r="M32" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N32" s="4" t="str">
         <f>IF(M32="","",IF(ISNUMBER(M32),IF(M32&lt;'Scoring Methodology'!$F$16,"Low",IF(M32&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M32&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -9639,21 +9787,23 @@
       <c r="U32" s="3"/>
       <c r="V32" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W32" s="4" t="str">
         <f>IF(V32="","",IF(ISNUMBER(V32),IF(V32&lt;'Scoring Methodology'!$F$16,"Low",IF(V32&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V32&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X32" s="3"/>
-      <c r="Y32" s="4" t="n">
+      <c r="Y32" s="4">
         <f>IF(E32="",0,IF(AND(OR(Dashboard!$L$7="All",Q32=Dashboard!$L$7),OR(Dashboard!$T$7="All",N32=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -9664,9 +9814,11 @@
       <c r="L33" s="3"/>
       <c r="M33" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N33" s="4" t="str">
         <f>IF(M33="","",IF(ISNUMBER(M33),IF(M33&lt;'Scoring Methodology'!$F$16,"Low",IF(M33&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M33&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -9677,21 +9829,23 @@
       <c r="U33" s="3"/>
       <c r="V33" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W33" s="4" t="str">
         <f>IF(V33="","",IF(ISNUMBER(V33),IF(V33&lt;'Scoring Methodology'!$F$16,"Low",IF(V33&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V33&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X33" s="3"/>
-      <c r="Y33" s="4" t="n">
+      <c r="Y33" s="4">
         <f>IF(E33="",0,IF(AND(OR(Dashboard!$L$7="All",Q33=Dashboard!$L$7),OR(Dashboard!$T$7="All",N33=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
+      <c r="A34" s="54"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -9702,9 +9856,11 @@
       <c r="L34" s="3"/>
       <c r="M34" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N34" s="4" t="str">
         <f>IF(M34="","",IF(ISNUMBER(M34),IF(M34&lt;'Scoring Methodology'!$F$16,"Low",IF(M34&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M34&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -9715,21 +9871,23 @@
       <c r="U34" s="3"/>
       <c r="V34" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W34" s="4" t="str">
         <f>IF(V34="","",IF(ISNUMBER(V34),IF(V34&lt;'Scoring Methodology'!$F$16,"Low",IF(V34&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V34&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X34" s="3"/>
-      <c r="Y34" s="4" t="n">
+      <c r="Y34" s="4">
         <f>IF(E34="",0,IF(AND(OR(Dashboard!$L$7="All",Q34=Dashboard!$L$7),OR(Dashboard!$T$7="All",N34=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
+      <c r="A35" s="54"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -9740,9 +9898,11 @@
       <c r="L35" s="3"/>
       <c r="M35" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N35" s="4" t="str">
         <f>IF(M35="","",IF(ISNUMBER(M35),IF(M35&lt;'Scoring Methodology'!$F$16,"Low",IF(M35&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M35&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
@@ -9753,21 +9913,23 @@
       <c r="U35" s="3"/>
       <c r="V35" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W35" s="4" t="str">
         <f>IF(V35="","",IF(ISNUMBER(V35),IF(V35&lt;'Scoring Methodology'!$F$16,"Low",IF(V35&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V35&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X35" s="3"/>
-      <c r="Y35" s="4" t="n">
+      <c r="Y35" s="4">
         <f>IF(E35="",0,IF(AND(OR(Dashboard!$L$7="All",Q35=Dashboard!$L$7),OR(Dashboard!$T$7="All",N35=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
+      <c r="A36" s="54"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -9778,9 +9940,11 @@
       <c r="L36" s="3"/>
       <c r="M36" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N36" s="4" t="str">
         <f>IF(M36="","",IF(ISNUMBER(M36),IF(M36&lt;'Scoring Methodology'!$F$16,"Low",IF(M36&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M36&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
@@ -9791,21 +9955,23 @@
       <c r="U36" s="3"/>
       <c r="V36" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W36" s="4" t="str">
         <f>IF(V36="","",IF(ISNUMBER(V36),IF(V36&lt;'Scoring Methodology'!$F$16,"Low",IF(V36&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V36&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X36" s="3"/>
-      <c r="Y36" s="4" t="n">
+      <c r="Y36" s="4">
         <f>IF(E36="",0,IF(AND(OR(Dashboard!$L$7="All",Q36=Dashboard!$L$7),OR(Dashboard!$T$7="All",N36=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
+      <c r="A37" s="54"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -9816,9 +9982,11 @@
       <c r="L37" s="3"/>
       <c r="M37" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N37" s="4" t="str">
         <f>IF(M37="","",IF(ISNUMBER(M37),IF(M37&lt;'Scoring Methodology'!$F$16,"Low",IF(M37&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M37&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
@@ -9829,21 +9997,23 @@
       <c r="U37" s="3"/>
       <c r="V37" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W37" s="4" t="str">
         <f>IF(V37="","",IF(ISNUMBER(V37),IF(V37&lt;'Scoring Methodology'!$F$16,"Low",IF(V37&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V37&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X37" s="3"/>
-      <c r="Y37" s="4" t="n">
+      <c r="Y37" s="4">
         <f>IF(E37="",0,IF(AND(OR(Dashboard!$L$7="All",Q37=Dashboard!$L$7),OR(Dashboard!$T$7="All",N37=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -9854,9 +10024,11 @@
       <c r="L38" s="3"/>
       <c r="M38" s="4" t="str">
         <f t="shared" si="0"/>
+        <v/>
       </c>
       <c r="N38" s="4" t="str">
         <f>IF(M38="","",IF(ISNUMBER(M38),IF(M38&lt;'Scoring Methodology'!$F$16,"Low",IF(M38&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M38&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
@@ -9867,21 +10039,23 @@
       <c r="U38" s="3"/>
       <c r="V38" s="4" t="str">
         <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W38" s="4" t="str">
         <f>IF(V38="","",IF(ISNUMBER(V38),IF(V38&lt;'Scoring Methodology'!$F$16,"Low",IF(V38&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V38&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X38" s="3"/>
-      <c r="Y38" s="4" t="n">
+      <c r="Y38" s="4">
         <f>IF(E38="",0,IF(AND(OR(Dashboard!$L$7="All",Q38=Dashboard!$L$7),OR(Dashboard!$T$7="All",N38=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
+      <c r="A39" s="54"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -9892,9 +10066,11 @@
       <c r="L39" s="3"/>
       <c r="M39" s="4" t="str">
         <f t="shared" ref="M39:M70" si="2">IF(E39="","",IF(OR(K39="",L39=""),"",IF(AND(ISNUMBER(K39),ISNUMBER(L39),K39&gt;=1,K39&lt;=5,L39&gt;=1,L39&lt;=5,MOD(K39,1)=0,MOD(L39,1)=0),K39*L39,"Invalid input")))</f>
+        <v/>
       </c>
       <c r="N39" s="4" t="str">
         <f>IF(M39="","",IF(ISNUMBER(M39),IF(M39&lt;'Scoring Methodology'!$F$16,"Low",IF(M39&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M39&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -9905,21 +10081,23 @@
       <c r="U39" s="3"/>
       <c r="V39" s="4" t="str">
         <f t="shared" ref="V39:V70" si="3">IF(E39="","",IF(OR(T39="",U39=""),"",IF(AND(ISNUMBER(T39),ISNUMBER(U39),T39&gt;=1,T39&lt;=5,U39&gt;=1,U39&lt;=5,MOD(T39,1)=0,MOD(U39,1)=0),T39*U39,"Invalid input")))</f>
+        <v/>
       </c>
       <c r="W39" s="4" t="str">
         <f>IF(V39="","",IF(ISNUMBER(V39),IF(V39&lt;'Scoring Methodology'!$F$16,"Low",IF(V39&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V39&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X39" s="3"/>
-      <c r="Y39" s="4" t="n">
+      <c r="Y39" s="4">
         <f>IF(E39="",0,IF(AND(OR(Dashboard!$L$7="All",Q39=Dashboard!$L$7),OR(Dashboard!$T$7="All",N39=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
+      <c r="A40" s="54"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -9930,9 +10108,11 @@
       <c r="L40" s="3"/>
       <c r="M40" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N40" s="4" t="str">
         <f>IF(M40="","",IF(ISNUMBER(M40),IF(M40&lt;'Scoring Methodology'!$F$16,"Low",IF(M40&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M40&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -9943,21 +10123,23 @@
       <c r="U40" s="3"/>
       <c r="V40" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W40" s="4" t="str">
         <f>IF(V40="","",IF(ISNUMBER(V40),IF(V40&lt;'Scoring Methodology'!$F$16,"Low",IF(V40&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V40&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X40" s="3"/>
-      <c r="Y40" s="4" t="n">
+      <c r="Y40" s="4">
         <f>IF(E40="",0,IF(AND(OR(Dashboard!$L$7="All",Q40=Dashboard!$L$7),OR(Dashboard!$T$7="All",N40=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -9968,9 +10150,11 @@
       <c r="L41" s="3"/>
       <c r="M41" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N41" s="4" t="str">
         <f>IF(M41="","",IF(ISNUMBER(M41),IF(M41&lt;'Scoring Methodology'!$F$16,"Low",IF(M41&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M41&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
@@ -9981,21 +10165,23 @@
       <c r="U41" s="3"/>
       <c r="V41" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W41" s="4" t="str">
         <f>IF(V41="","",IF(ISNUMBER(V41),IF(V41&lt;'Scoring Methodology'!$F$16,"Low",IF(V41&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V41&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X41" s="3"/>
-      <c r="Y41" s="4" t="n">
+      <c r="Y41" s="4">
         <f>IF(E41="",0,IF(AND(OR(Dashboard!$L$7="All",Q41=Dashboard!$L$7),OR(Dashboard!$T$7="All",N41=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -10006,9 +10192,11 @@
       <c r="L42" s="3"/>
       <c r="M42" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N42" s="4" t="str">
         <f>IF(M42="","",IF(ISNUMBER(M42),IF(M42&lt;'Scoring Methodology'!$F$16,"Low",IF(M42&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M42&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
@@ -10019,21 +10207,23 @@
       <c r="U42" s="3"/>
       <c r="V42" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W42" s="4" t="str">
         <f>IF(V42="","",IF(ISNUMBER(V42),IF(V42&lt;'Scoring Methodology'!$F$16,"Low",IF(V42&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V42&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X42" s="3"/>
-      <c r="Y42" s="4" t="n">
+      <c r="Y42" s="4">
         <f>IF(E42="",0,IF(AND(OR(Dashboard!$L$7="All",Q42=Dashboard!$L$7),OR(Dashboard!$T$7="All",N42=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
+      <c r="A43" s="54"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -10044,9 +10234,11 @@
       <c r="L43" s="3"/>
       <c r="M43" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N43" s="4" t="str">
         <f>IF(M43="","",IF(ISNUMBER(M43),IF(M43&lt;'Scoring Methodology'!$F$16,"Low",IF(M43&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M43&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -10057,21 +10249,23 @@
       <c r="U43" s="3"/>
       <c r="V43" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W43" s="4" t="str">
         <f>IF(V43="","",IF(ISNUMBER(V43),IF(V43&lt;'Scoring Methodology'!$F$16,"Low",IF(V43&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V43&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X43" s="3"/>
-      <c r="Y43" s="4" t="n">
+      <c r="Y43" s="4">
         <f>IF(E43="",0,IF(AND(OR(Dashboard!$L$7="All",Q43=Dashboard!$L$7),OR(Dashboard!$T$7="All",N43=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -10082,9 +10276,11 @@
       <c r="L44" s="3"/>
       <c r="M44" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N44" s="4" t="str">
         <f>IF(M44="","",IF(ISNUMBER(M44),IF(M44&lt;'Scoring Methodology'!$F$16,"Low",IF(M44&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M44&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
@@ -10095,21 +10291,23 @@
       <c r="U44" s="3"/>
       <c r="V44" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W44" s="4" t="str">
         <f>IF(V44="","",IF(ISNUMBER(V44),IF(V44&lt;'Scoring Methodology'!$F$16,"Low",IF(V44&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V44&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X44" s="3"/>
-      <c r="Y44" s="4" t="n">
+      <c r="Y44" s="4">
         <f>IF(E44="",0,IF(AND(OR(Dashboard!$L$7="All",Q44=Dashboard!$L$7),OR(Dashboard!$T$7="All",N44=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -10120,9 +10318,11 @@
       <c r="L45" s="3"/>
       <c r="M45" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N45" s="4" t="str">
         <f>IF(M45="","",IF(ISNUMBER(M45),IF(M45&lt;'Scoring Methodology'!$F$16,"Low",IF(M45&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M45&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
@@ -10133,21 +10333,23 @@
       <c r="U45" s="3"/>
       <c r="V45" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W45" s="4" t="str">
         <f>IF(V45="","",IF(ISNUMBER(V45),IF(V45&lt;'Scoring Methodology'!$F$16,"Low",IF(V45&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V45&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X45" s="3"/>
-      <c r="Y45" s="4" t="n">
+      <c r="Y45" s="4">
         <f>IF(E45="",0,IF(AND(OR(Dashboard!$L$7="All",Q45=Dashboard!$L$7),OR(Dashboard!$T$7="All",N45=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -10158,9 +10360,11 @@
       <c r="L46" s="3"/>
       <c r="M46" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N46" s="4" t="str">
         <f>IF(M46="","",IF(ISNUMBER(M46),IF(M46&lt;'Scoring Methodology'!$F$16,"Low",IF(M46&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M46&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
@@ -10171,21 +10375,23 @@
       <c r="U46" s="3"/>
       <c r="V46" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W46" s="4" t="str">
         <f>IF(V46="","",IF(ISNUMBER(V46),IF(V46&lt;'Scoring Methodology'!$F$16,"Low",IF(V46&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V46&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X46" s="3"/>
-      <c r="Y46" s="4" t="n">
+      <c r="Y46" s="4">
         <f>IF(E46="",0,IF(AND(OR(Dashboard!$L$7="All",Q46=Dashboard!$L$7),OR(Dashboard!$T$7="All",N46=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -10196,9 +10402,11 @@
       <c r="L47" s="3"/>
       <c r="M47" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N47" s="4" t="str">
         <f>IF(M47="","",IF(ISNUMBER(M47),IF(M47&lt;'Scoring Methodology'!$F$16,"Low",IF(M47&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M47&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
@@ -10209,21 +10417,23 @@
       <c r="U47" s="3"/>
       <c r="V47" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W47" s="4" t="str">
         <f>IF(V47="","",IF(ISNUMBER(V47),IF(V47&lt;'Scoring Methodology'!$F$16,"Low",IF(V47&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V47&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X47" s="3"/>
-      <c r="Y47" s="4" t="n">
+      <c r="Y47" s="4">
         <f>IF(E47="",0,IF(AND(OR(Dashboard!$L$7="All",Q47=Dashboard!$L$7),OR(Dashboard!$T$7="All",N47=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -10234,9 +10444,11 @@
       <c r="L48" s="3"/>
       <c r="M48" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N48" s="4" t="str">
         <f>IF(M48="","",IF(ISNUMBER(M48),IF(M48&lt;'Scoring Methodology'!$F$16,"Low",IF(M48&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M48&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
@@ -10247,21 +10459,23 @@
       <c r="U48" s="3"/>
       <c r="V48" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W48" s="4" t="str">
         <f>IF(V48="","",IF(ISNUMBER(V48),IF(V48&lt;'Scoring Methodology'!$F$16,"Low",IF(V48&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V48&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X48" s="3"/>
-      <c r="Y48" s="4" t="n">
+      <c r="Y48" s="4">
         <f>IF(E48="",0,IF(AND(OR(Dashboard!$L$7="All",Q48=Dashboard!$L$7),OR(Dashboard!$T$7="All",N48=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A49" s="18"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -10272,9 +10486,11 @@
       <c r="L49" s="3"/>
       <c r="M49" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N49" s="4" t="str">
         <f>IF(M49="","",IF(ISNUMBER(M49),IF(M49&lt;'Scoring Methodology'!$F$16,"Low",IF(M49&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M49&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
@@ -10285,21 +10501,23 @@
       <c r="U49" s="3"/>
       <c r="V49" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W49" s="4" t="str">
         <f>IF(V49="","",IF(ISNUMBER(V49),IF(V49&lt;'Scoring Methodology'!$F$16,"Low",IF(V49&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V49&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X49" s="3"/>
-      <c r="Y49" s="4" t="n">
+      <c r="Y49" s="4">
         <f>IF(E49="",0,IF(AND(OR(Dashboard!$L$7="All",Q49=Dashboard!$L$7),OR(Dashboard!$T$7="All",N49=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A50" s="18"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -10310,9 +10528,11 @@
       <c r="L50" s="3"/>
       <c r="M50" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N50" s="4" t="str">
         <f>IF(M50="","",IF(ISNUMBER(M50),IF(M50&lt;'Scoring Methodology'!$F$16,"Low",IF(M50&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M50&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -10323,21 +10543,23 @@
       <c r="U50" s="3"/>
       <c r="V50" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W50" s="4" t="str">
         <f>IF(V50="","",IF(ISNUMBER(V50),IF(V50&lt;'Scoring Methodology'!$F$16,"Low",IF(V50&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V50&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X50" s="3"/>
-      <c r="Y50" s="4" t="n">
+      <c r="Y50" s="4">
         <f>IF(E50="",0,IF(AND(OR(Dashboard!$L$7="All",Q50=Dashboard!$L$7),OR(Dashboard!$T$7="All",N50=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A51" s="18"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
+      <c r="A51" s="54"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -10348,9 +10570,11 @@
       <c r="L51" s="3"/>
       <c r="M51" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N51" s="4" t="str">
         <f>IF(M51="","",IF(ISNUMBER(M51),IF(M51&lt;'Scoring Methodology'!$F$16,"Low",IF(M51&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M51&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
@@ -10361,21 +10585,23 @@
       <c r="U51" s="3"/>
       <c r="V51" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W51" s="4" t="str">
         <f>IF(V51="","",IF(ISNUMBER(V51),IF(V51&lt;'Scoring Methodology'!$F$16,"Low",IF(V51&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V51&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X51" s="3"/>
-      <c r="Y51" s="4" t="n">
+      <c r="Y51" s="4">
         <f>IF(E51="",0,IF(AND(OR(Dashboard!$L$7="All",Q51=Dashboard!$L$7),OR(Dashboard!$T$7="All",N51=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A52" s="18"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
+      <c r="A52" s="54"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -10386,9 +10612,11 @@
       <c r="L52" s="3"/>
       <c r="M52" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N52" s="4" t="str">
         <f>IF(M52="","",IF(ISNUMBER(M52),IF(M52&lt;'Scoring Methodology'!$F$16,"Low",IF(M52&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M52&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
@@ -10399,21 +10627,23 @@
       <c r="U52" s="3"/>
       <c r="V52" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W52" s="4" t="str">
         <f>IF(V52="","",IF(ISNUMBER(V52),IF(V52&lt;'Scoring Methodology'!$F$16,"Low",IF(V52&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V52&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X52" s="3"/>
-      <c r="Y52" s="4" t="n">
+      <c r="Y52" s="4">
         <f>IF(E52="",0,IF(AND(OR(Dashboard!$L$7="All",Q52=Dashboard!$L$7),OR(Dashboard!$T$7="All",N52=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A53" s="18"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -10424,9 +10654,11 @@
       <c r="L53" s="3"/>
       <c r="M53" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N53" s="4" t="str">
         <f>IF(M53="","",IF(ISNUMBER(M53),IF(M53&lt;'Scoring Methodology'!$F$16,"Low",IF(M53&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M53&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
@@ -10437,21 +10669,23 @@
       <c r="U53" s="3"/>
       <c r="V53" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W53" s="4" t="str">
         <f>IF(V53="","",IF(ISNUMBER(V53),IF(V53&lt;'Scoring Methodology'!$F$16,"Low",IF(V53&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V53&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X53" s="3"/>
-      <c r="Y53" s="4" t="n">
+      <c r="Y53" s="4">
         <f>IF(E53="",0,IF(AND(OR(Dashboard!$L$7="All",Q53=Dashboard!$L$7),OR(Dashboard!$T$7="All",N53=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A54" s="18"/>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -10462,9 +10696,11 @@
       <c r="L54" s="3"/>
       <c r="M54" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N54" s="4" t="str">
         <f>IF(M54="","",IF(ISNUMBER(M54),IF(M54&lt;'Scoring Methodology'!$F$16,"Low",IF(M54&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M54&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
@@ -10475,21 +10711,23 @@
       <c r="U54" s="3"/>
       <c r="V54" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W54" s="4" t="str">
         <f>IF(V54="","",IF(ISNUMBER(V54),IF(V54&lt;'Scoring Methodology'!$F$16,"Low",IF(V54&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V54&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X54" s="3"/>
-      <c r="Y54" s="4" t="n">
+      <c r="Y54" s="4">
         <f>IF(E54="",0,IF(AND(OR(Dashboard!$L$7="All",Q54=Dashboard!$L$7),OR(Dashboard!$T$7="All",N54=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A55" s="18"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -10500,9 +10738,11 @@
       <c r="L55" s="3"/>
       <c r="M55" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N55" s="4" t="str">
         <f>IF(M55="","",IF(ISNUMBER(M55),IF(M55&lt;'Scoring Methodology'!$F$16,"Low",IF(M55&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M55&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
@@ -10513,21 +10753,23 @@
       <c r="U55" s="3"/>
       <c r="V55" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W55" s="4" t="str">
         <f>IF(V55="","",IF(ISNUMBER(V55),IF(V55&lt;'Scoring Methodology'!$F$16,"Low",IF(V55&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V55&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X55" s="3"/>
-      <c r="Y55" s="4" t="n">
+      <c r="Y55" s="4">
         <f>IF(E55="",0,IF(AND(OR(Dashboard!$L$7="All",Q55=Dashboard!$L$7),OR(Dashboard!$T$7="All",N55=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A56" s="18"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
@@ -10538,9 +10780,11 @@
       <c r="L56" s="3"/>
       <c r="M56" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N56" s="4" t="str">
         <f>IF(M56="","",IF(ISNUMBER(M56),IF(M56&lt;'Scoring Methodology'!$F$16,"Low",IF(M56&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M56&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
@@ -10551,21 +10795,23 @@
       <c r="U56" s="3"/>
       <c r="V56" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W56" s="4" t="str">
         <f>IF(V56="","",IF(ISNUMBER(V56),IF(V56&lt;'Scoring Methodology'!$F$16,"Low",IF(V56&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V56&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X56" s="3"/>
-      <c r="Y56" s="4" t="n">
+      <c r="Y56" s="4">
         <f>IF(E56="",0,IF(AND(OR(Dashboard!$L$7="All",Q56=Dashboard!$L$7),OR(Dashboard!$T$7="All",N56=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A57" s="18"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
+      <c r="A57" s="54"/>
+      <c r="B57" s="54"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -10576,9 +10822,11 @@
       <c r="L57" s="3"/>
       <c r="M57" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N57" s="4" t="str">
         <f>IF(M57="","",IF(ISNUMBER(M57),IF(M57&lt;'Scoring Methodology'!$F$16,"Low",IF(M57&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M57&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
@@ -10589,21 +10837,23 @@
       <c r="U57" s="3"/>
       <c r="V57" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W57" s="4" t="str">
         <f>IF(V57="","",IF(ISNUMBER(V57),IF(V57&lt;'Scoring Methodology'!$F$16,"Low",IF(V57&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V57&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X57" s="3"/>
-      <c r="Y57" s="4" t="n">
+      <c r="Y57" s="4">
         <f>IF(E57="",0,IF(AND(OR(Dashboard!$L$7="All",Q57=Dashboard!$L$7),OR(Dashboard!$T$7="All",N57=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
+      <c r="A58" s="54"/>
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
@@ -10614,9 +10864,11 @@
       <c r="L58" s="3"/>
       <c r="M58" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N58" s="4" t="str">
         <f>IF(M58="","",IF(ISNUMBER(M58),IF(M58&lt;'Scoring Methodology'!$F$16,"Low",IF(M58&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M58&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
@@ -10627,21 +10879,23 @@
       <c r="U58" s="3"/>
       <c r="V58" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W58" s="4" t="str">
         <f>IF(V58="","",IF(ISNUMBER(V58),IF(V58&lt;'Scoring Methodology'!$F$16,"Low",IF(V58&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V58&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X58" s="3"/>
-      <c r="Y58" s="4" t="n">
+      <c r="Y58" s="4">
         <f>IF(E58="",0,IF(AND(OR(Dashboard!$L$7="All",Q58=Dashboard!$L$7),OR(Dashboard!$T$7="All",N58=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
+      <c r="A59" s="54"/>
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
@@ -10652,9 +10906,11 @@
       <c r="L59" s="3"/>
       <c r="M59" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N59" s="4" t="str">
         <f>IF(M59="","",IF(ISNUMBER(M59),IF(M59&lt;'Scoring Methodology'!$F$16,"Low",IF(M59&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M59&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
@@ -10665,21 +10921,23 @@
       <c r="U59" s="3"/>
       <c r="V59" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W59" s="4" t="str">
         <f>IF(V59="","",IF(ISNUMBER(V59),IF(V59&lt;'Scoring Methodology'!$F$16,"Low",IF(V59&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V59&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X59" s="3"/>
-      <c r="Y59" s="4" t="n">
+      <c r="Y59" s="4">
         <f>IF(E59="",0,IF(AND(OR(Dashboard!$L$7="All",Q59=Dashboard!$L$7),OR(Dashboard!$T$7="All",N59=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A60" s="18"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
+      <c r="A60" s="54"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
@@ -10690,9 +10948,11 @@
       <c r="L60" s="3"/>
       <c r="M60" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N60" s="4" t="str">
         <f>IF(M60="","",IF(ISNUMBER(M60),IF(M60&lt;'Scoring Methodology'!$F$16,"Low",IF(M60&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M60&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
@@ -10703,21 +10963,23 @@
       <c r="U60" s="3"/>
       <c r="V60" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W60" s="4" t="str">
         <f>IF(V60="","",IF(ISNUMBER(V60),IF(V60&lt;'Scoring Methodology'!$F$16,"Low",IF(V60&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V60&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X60" s="3"/>
-      <c r="Y60" s="4" t="n">
+      <c r="Y60" s="4">
         <f>IF(E60="",0,IF(AND(OR(Dashboard!$L$7="All",Q60=Dashboard!$L$7),OR(Dashboard!$T$7="All",N60=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A61" s="18"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
+      <c r="A61" s="54"/>
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -10728,9 +10990,11 @@
       <c r="L61" s="3"/>
       <c r="M61" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N61" s="4" t="str">
         <f>IF(M61="","",IF(ISNUMBER(M61),IF(M61&lt;'Scoring Methodology'!$F$16,"Low",IF(M61&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M61&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
@@ -10741,21 +11005,23 @@
       <c r="U61" s="3"/>
       <c r="V61" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W61" s="4" t="str">
         <f>IF(V61="","",IF(ISNUMBER(V61),IF(V61&lt;'Scoring Methodology'!$F$16,"Low",IF(V61&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V61&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X61" s="3"/>
-      <c r="Y61" s="4" t="n">
+      <c r="Y61" s="4">
         <f>IF(E61="",0,IF(AND(OR(Dashboard!$L$7="All",Q61=Dashboard!$L$7),OR(Dashboard!$T$7="All",N61=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
+      <c r="A62" s="54"/>
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
@@ -10766,9 +11032,11 @@
       <c r="L62" s="3"/>
       <c r="M62" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N62" s="4" t="str">
         <f>IF(M62="","",IF(ISNUMBER(M62),IF(M62&lt;'Scoring Methodology'!$F$16,"Low",IF(M62&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M62&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
@@ -10779,21 +11047,23 @@
       <c r="U62" s="3"/>
       <c r="V62" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W62" s="4" t="str">
         <f>IF(V62="","",IF(ISNUMBER(V62),IF(V62&lt;'Scoring Methodology'!$F$16,"Low",IF(V62&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V62&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X62" s="3"/>
-      <c r="Y62" s="4" t="n">
+      <c r="Y62" s="4">
         <f>IF(E62="",0,IF(AND(OR(Dashboard!$L$7="All",Q62=Dashboard!$L$7),OR(Dashboard!$T$7="All",N62=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A63" s="18"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
+      <c r="A63" s="54"/>
+      <c r="B63" s="54"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
@@ -10804,9 +11074,11 @@
       <c r="L63" s="3"/>
       <c r="M63" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N63" s="4" t="str">
         <f>IF(M63="","",IF(ISNUMBER(M63),IF(M63&lt;'Scoring Methodology'!$F$16,"Low",IF(M63&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M63&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
@@ -10817,21 +11089,23 @@
       <c r="U63" s="3"/>
       <c r="V63" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W63" s="4" t="str">
         <f>IF(V63="","",IF(ISNUMBER(V63),IF(V63&lt;'Scoring Methodology'!$F$16,"Low",IF(V63&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V63&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X63" s="3"/>
-      <c r="Y63" s="4" t="n">
+      <c r="Y63" s="4">
         <f>IF(E63="",0,IF(AND(OR(Dashboard!$L$7="All",Q63=Dashboard!$L$7),OR(Dashboard!$T$7="All",N63=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
+      <c r="A64" s="54"/>
+      <c r="B64" s="54"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
@@ -10842,9 +11116,11 @@
       <c r="L64" s="3"/>
       <c r="M64" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N64" s="4" t="str">
         <f>IF(M64="","",IF(ISNUMBER(M64),IF(M64&lt;'Scoring Methodology'!$F$16,"Low",IF(M64&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M64&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
@@ -10855,21 +11131,23 @@
       <c r="U64" s="3"/>
       <c r="V64" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W64" s="4" t="str">
         <f>IF(V64="","",IF(ISNUMBER(V64),IF(V64&lt;'Scoring Methodology'!$F$16,"Low",IF(V64&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V64&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X64" s="3"/>
-      <c r="Y64" s="4" t="n">
+      <c r="Y64" s="4">
         <f>IF(E64="",0,IF(AND(OR(Dashboard!$L$7="All",Q64=Dashboard!$L$7),OR(Dashboard!$T$7="All",N64=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
+      <c r="A65" s="54"/>
+      <c r="B65" s="54"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -10880,9 +11158,11 @@
       <c r="L65" s="3"/>
       <c r="M65" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N65" s="4" t="str">
         <f>IF(M65="","",IF(ISNUMBER(M65),IF(M65&lt;'Scoring Methodology'!$F$16,"Low",IF(M65&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M65&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -10893,21 +11173,23 @@
       <c r="U65" s="3"/>
       <c r="V65" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W65" s="4" t="str">
         <f>IF(V65="","",IF(ISNUMBER(V65),IF(V65&lt;'Scoring Methodology'!$F$16,"Low",IF(V65&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V65&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X65" s="3"/>
-      <c r="Y65" s="4" t="n">
+      <c r="Y65" s="4">
         <f>IF(E65="",0,IF(AND(OR(Dashboard!$L$7="All",Q65=Dashboard!$L$7),OR(Dashboard!$T$7="All",N65=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A66" s="18"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
+      <c r="A66" s="54"/>
+      <c r="B66" s="54"/>
+      <c r="C66" s="54"/>
+      <c r="D66" s="54"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -10918,9 +11200,11 @@
       <c r="L66" s="3"/>
       <c r="M66" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N66" s="4" t="str">
         <f>IF(M66="","",IF(ISNUMBER(M66),IF(M66&lt;'Scoring Methodology'!$F$16,"Low",IF(M66&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M66&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
@@ -10931,21 +11215,23 @@
       <c r="U66" s="3"/>
       <c r="V66" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W66" s="4" t="str">
         <f>IF(V66="","",IF(ISNUMBER(V66),IF(V66&lt;'Scoring Methodology'!$F$16,"Low",IF(V66&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V66&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X66" s="3"/>
-      <c r="Y66" s="4" t="n">
+      <c r="Y66" s="4">
         <f>IF(E66="",0,IF(AND(OR(Dashboard!$L$7="All",Q66=Dashboard!$L$7),OR(Dashboard!$T$7="All",N66=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A67" s="18"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="18"/>
+      <c r="A67" s="54"/>
+      <c r="B67" s="54"/>
+      <c r="C67" s="54"/>
+      <c r="D67" s="54"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -10956,9 +11242,11 @@
       <c r="L67" s="3"/>
       <c r="M67" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N67" s="4" t="str">
         <f>IF(M67="","",IF(ISNUMBER(M67),IF(M67&lt;'Scoring Methodology'!$F$16,"Low",IF(M67&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M67&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
@@ -10969,21 +11257,23 @@
       <c r="U67" s="3"/>
       <c r="V67" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W67" s="4" t="str">
         <f>IF(V67="","",IF(ISNUMBER(V67),IF(V67&lt;'Scoring Methodology'!$F$16,"Low",IF(V67&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V67&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X67" s="3"/>
-      <c r="Y67" s="4" t="n">
+      <c r="Y67" s="4">
         <f>IF(E67="",0,IF(AND(OR(Dashboard!$L$7="All",Q67=Dashboard!$L$7),OR(Dashboard!$T$7="All",N67=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
+      <c r="A68" s="54"/>
+      <c r="B68" s="54"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -10994,9 +11284,11 @@
       <c r="L68" s="3"/>
       <c r="M68" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N68" s="4" t="str">
         <f>IF(M68="","",IF(ISNUMBER(M68),IF(M68&lt;'Scoring Methodology'!$F$16,"Low",IF(M68&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M68&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
@@ -11007,21 +11299,23 @@
       <c r="U68" s="3"/>
       <c r="V68" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W68" s="4" t="str">
         <f>IF(V68="","",IF(ISNUMBER(V68),IF(V68&lt;'Scoring Methodology'!$F$16,"Low",IF(V68&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V68&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X68" s="3"/>
-      <c r="Y68" s="4" t="n">
+      <c r="Y68" s="4">
         <f>IF(E68="",0,IF(AND(OR(Dashboard!$L$7="All",Q68=Dashboard!$L$7),OR(Dashboard!$T$7="All",N68=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A69" s="18"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
+      <c r="A69" s="54"/>
+      <c r="B69" s="54"/>
+      <c r="C69" s="54"/>
+      <c r="D69" s="54"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -11032,9 +11326,11 @@
       <c r="L69" s="3"/>
       <c r="M69" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N69" s="4" t="str">
         <f>IF(M69="","",IF(ISNUMBER(M69),IF(M69&lt;'Scoring Methodology'!$F$16,"Low",IF(M69&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M69&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
@@ -11045,21 +11341,23 @@
       <c r="U69" s="3"/>
       <c r="V69" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W69" s="4" t="str">
         <f>IF(V69="","",IF(ISNUMBER(V69),IF(V69&lt;'Scoring Methodology'!$F$16,"Low",IF(V69&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V69&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X69" s="3"/>
-      <c r="Y69" s="4" t="n">
+      <c r="Y69" s="4">
         <f>IF(E69="",0,IF(AND(OR(Dashboard!$L$7="All",Q69=Dashboard!$L$7),OR(Dashboard!$T$7="All",N69=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A70" s="18"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
+      <c r="A70" s="54"/>
+      <c r="B70" s="54"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -11070,9 +11368,11 @@
       <c r="L70" s="3"/>
       <c r="M70" s="4" t="str">
         <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="N70" s="4" t="str">
         <f>IF(M70="","",IF(ISNUMBER(M70),IF(M70&lt;'Scoring Methodology'!$F$16,"Low",IF(M70&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M70&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O70" s="3"/>
       <c r="P70" s="3"/>
@@ -11083,21 +11383,23 @@
       <c r="U70" s="3"/>
       <c r="V70" s="4" t="str">
         <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="W70" s="4" t="str">
         <f>IF(V70="","",IF(ISNUMBER(V70),IF(V70&lt;'Scoring Methodology'!$F$16,"Low",IF(V70&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V70&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X70" s="3"/>
-      <c r="Y70" s="4" t="n">
+      <c r="Y70" s="4">
         <f>IF(E70="",0,IF(AND(OR(Dashboard!$L$7="All",Q70=Dashboard!$L$7),OR(Dashboard!$T$7="All",N70=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A71" s="18"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
+      <c r="A71" s="54"/>
+      <c r="B71" s="54"/>
+      <c r="C71" s="54"/>
+      <c r="D71" s="54"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -11108,9 +11410,11 @@
       <c r="L71" s="3"/>
       <c r="M71" s="4" t="str">
         <f t="shared" ref="M71:M102" si="4">IF(E71="","",IF(OR(K71="",L71=""),"",IF(AND(ISNUMBER(K71),ISNUMBER(L71),K71&gt;=1,K71&lt;=5,L71&gt;=1,L71&lt;=5,MOD(K71,1)=0,MOD(L71,1)=0),K71*L71,"Invalid input")))</f>
+        <v/>
       </c>
       <c r="N71" s="4" t="str">
         <f>IF(M71="","",IF(ISNUMBER(M71),IF(M71&lt;'Scoring Methodology'!$F$16,"Low",IF(M71&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M71&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
@@ -11121,21 +11425,23 @@
       <c r="U71" s="3"/>
       <c r="V71" s="4" t="str">
         <f t="shared" ref="V71:V102" si="5">IF(E71="","",IF(OR(T71="",U71=""),"",IF(AND(ISNUMBER(T71),ISNUMBER(U71),T71&gt;=1,T71&lt;=5,U71&gt;=1,U71&lt;=5,MOD(T71,1)=0,MOD(U71,1)=0),T71*U71,"Invalid input")))</f>
+        <v/>
       </c>
       <c r="W71" s="4" t="str">
         <f>IF(V71="","",IF(ISNUMBER(V71),IF(V71&lt;'Scoring Methodology'!$F$16,"Low",IF(V71&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V71&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X71" s="3"/>
-      <c r="Y71" s="4" t="n">
+      <c r="Y71" s="4">
         <f>IF(E71="",0,IF(AND(OR(Dashboard!$L$7="All",Q71=Dashboard!$L$7),OR(Dashboard!$T$7="All",N71=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A72" s="18"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
+      <c r="A72" s="54"/>
+      <c r="B72" s="54"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -11146,9 +11452,11 @@
       <c r="L72" s="3"/>
       <c r="M72" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N72" s="4" t="str">
         <f>IF(M72="","",IF(ISNUMBER(M72),IF(M72&lt;'Scoring Methodology'!$F$16,"Low",IF(M72&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M72&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
@@ -11159,21 +11467,23 @@
       <c r="U72" s="3"/>
       <c r="V72" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W72" s="4" t="str">
         <f>IF(V72="","",IF(ISNUMBER(V72),IF(V72&lt;'Scoring Methodology'!$F$16,"Low",IF(V72&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V72&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X72" s="3"/>
-      <c r="Y72" s="4" t="n">
+      <c r="Y72" s="4">
         <f>IF(E72="",0,IF(AND(OR(Dashboard!$L$7="All",Q72=Dashboard!$L$7),OR(Dashboard!$T$7="All",N72=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A73" s="18"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
+      <c r="A73" s="54"/>
+      <c r="B73" s="54"/>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -11184,9 +11494,11 @@
       <c r="L73" s="3"/>
       <c r="M73" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N73" s="4" t="str">
         <f>IF(M73="","",IF(ISNUMBER(M73),IF(M73&lt;'Scoring Methodology'!$F$16,"Low",IF(M73&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M73&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
@@ -11197,21 +11509,23 @@
       <c r="U73" s="3"/>
       <c r="V73" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W73" s="4" t="str">
         <f>IF(V73="","",IF(ISNUMBER(V73),IF(V73&lt;'Scoring Methodology'!$F$16,"Low",IF(V73&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V73&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X73" s="3"/>
-      <c r="Y73" s="4" t="n">
+      <c r="Y73" s="4">
         <f>IF(E73="",0,IF(AND(OR(Dashboard!$L$7="All",Q73=Dashboard!$L$7),OR(Dashboard!$T$7="All",N73=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A74" s="18"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
+      <c r="A74" s="54"/>
+      <c r="B74" s="54"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
@@ -11222,9 +11536,11 @@
       <c r="L74" s="3"/>
       <c r="M74" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N74" s="4" t="str">
         <f>IF(M74="","",IF(ISNUMBER(M74),IF(M74&lt;'Scoring Methodology'!$F$16,"Low",IF(M74&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M74&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
@@ -11235,21 +11551,23 @@
       <c r="U74" s="3"/>
       <c r="V74" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W74" s="4" t="str">
         <f>IF(V74="","",IF(ISNUMBER(V74),IF(V74&lt;'Scoring Methodology'!$F$16,"Low",IF(V74&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V74&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X74" s="3"/>
-      <c r="Y74" s="4" t="n">
+      <c r="Y74" s="4">
         <f>IF(E74="",0,IF(AND(OR(Dashboard!$L$7="All",Q74=Dashboard!$L$7),OR(Dashboard!$T$7="All",N74=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A75" s="18"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
+      <c r="A75" s="54"/>
+      <c r="B75" s="54"/>
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
@@ -11260,9 +11578,11 @@
       <c r="L75" s="3"/>
       <c r="M75" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N75" s="4" t="str">
         <f>IF(M75="","",IF(ISNUMBER(M75),IF(M75&lt;'Scoring Methodology'!$F$16,"Low",IF(M75&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M75&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
@@ -11273,21 +11593,23 @@
       <c r="U75" s="3"/>
       <c r="V75" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W75" s="4" t="str">
         <f>IF(V75="","",IF(ISNUMBER(V75),IF(V75&lt;'Scoring Methodology'!$F$16,"Low",IF(V75&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V75&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X75" s="3"/>
-      <c r="Y75" s="4" t="n">
+      <c r="Y75" s="4">
         <f>IF(E75="",0,IF(AND(OR(Dashboard!$L$7="All",Q75=Dashboard!$L$7),OR(Dashboard!$T$7="All",N75=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A76" s="18"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
+      <c r="A76" s="54"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
@@ -11298,9 +11620,11 @@
       <c r="L76" s="3"/>
       <c r="M76" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N76" s="4" t="str">
         <f>IF(M76="","",IF(ISNUMBER(M76),IF(M76&lt;'Scoring Methodology'!$F$16,"Low",IF(M76&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M76&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
@@ -11311,21 +11635,23 @@
       <c r="U76" s="3"/>
       <c r="V76" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W76" s="4" t="str">
         <f>IF(V76="","",IF(ISNUMBER(V76),IF(V76&lt;'Scoring Methodology'!$F$16,"Low",IF(V76&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V76&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X76" s="3"/>
-      <c r="Y76" s="4" t="n">
+      <c r="Y76" s="4">
         <f>IF(E76="",0,IF(AND(OR(Dashboard!$L$7="All",Q76=Dashboard!$L$7),OR(Dashboard!$T$7="All",N76=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A77" s="18"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
+      <c r="A77" s="54"/>
+      <c r="B77" s="54"/>
+      <c r="C77" s="54"/>
+      <c r="D77" s="54"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -11336,9 +11662,11 @@
       <c r="L77" s="3"/>
       <c r="M77" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N77" s="4" t="str">
         <f>IF(M77="","",IF(ISNUMBER(M77),IF(M77&lt;'Scoring Methodology'!$F$16,"Low",IF(M77&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M77&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
@@ -11349,21 +11677,23 @@
       <c r="U77" s="3"/>
       <c r="V77" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W77" s="4" t="str">
         <f>IF(V77="","",IF(ISNUMBER(V77),IF(V77&lt;'Scoring Methodology'!$F$16,"Low",IF(V77&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V77&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X77" s="3"/>
-      <c r="Y77" s="4" t="n">
+      <c r="Y77" s="4">
         <f>IF(E77="",0,IF(AND(OR(Dashboard!$L$7="All",Q77=Dashboard!$L$7),OR(Dashboard!$T$7="All",N77=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A78" s="18"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
+      <c r="A78" s="54"/>
+      <c r="B78" s="54"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -11374,9 +11704,11 @@
       <c r="L78" s="3"/>
       <c r="M78" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N78" s="4" t="str">
         <f>IF(M78="","",IF(ISNUMBER(M78),IF(M78&lt;'Scoring Methodology'!$F$16,"Low",IF(M78&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M78&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
@@ -11387,21 +11719,23 @@
       <c r="U78" s="3"/>
       <c r="V78" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W78" s="4" t="str">
         <f>IF(V78="","",IF(ISNUMBER(V78),IF(V78&lt;'Scoring Methodology'!$F$16,"Low",IF(V78&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V78&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X78" s="3"/>
-      <c r="Y78" s="4" t="n">
+      <c r="Y78" s="4">
         <f>IF(E78="",0,IF(AND(OR(Dashboard!$L$7="All",Q78=Dashboard!$L$7),OR(Dashboard!$T$7="All",N78=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A79" s="18"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
+      <c r="A79" s="54"/>
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -11412,9 +11746,11 @@
       <c r="L79" s="3"/>
       <c r="M79" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N79" s="4" t="str">
         <f>IF(M79="","",IF(ISNUMBER(M79),IF(M79&lt;'Scoring Methodology'!$F$16,"Low",IF(M79&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M79&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
@@ -11425,21 +11761,23 @@
       <c r="U79" s="3"/>
       <c r="V79" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W79" s="4" t="str">
         <f>IF(V79="","",IF(ISNUMBER(V79),IF(V79&lt;'Scoring Methodology'!$F$16,"Low",IF(V79&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V79&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X79" s="3"/>
-      <c r="Y79" s="4" t="n">
+      <c r="Y79" s="4">
         <f>IF(E79="",0,IF(AND(OR(Dashboard!$L$7="All",Q79=Dashboard!$L$7),OR(Dashboard!$T$7="All",N79=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A80" s="18"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
+      <c r="A80" s="54"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -11450,9 +11788,11 @@
       <c r="L80" s="3"/>
       <c r="M80" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N80" s="4" t="str">
         <f>IF(M80="","",IF(ISNUMBER(M80),IF(M80&lt;'Scoring Methodology'!$F$16,"Low",IF(M80&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M80&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
@@ -11463,21 +11803,23 @@
       <c r="U80" s="3"/>
       <c r="V80" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W80" s="4" t="str">
         <f>IF(V80="","",IF(ISNUMBER(V80),IF(V80&lt;'Scoring Methodology'!$F$16,"Low",IF(V80&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V80&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X80" s="3"/>
-      <c r="Y80" s="4" t="n">
+      <c r="Y80" s="4">
         <f>IF(E80="",0,IF(AND(OR(Dashboard!$L$7="All",Q80=Dashboard!$L$7),OR(Dashboard!$T$7="All",N80=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A81" s="18"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
+      <c r="A81" s="54"/>
+      <c r="B81" s="54"/>
+      <c r="C81" s="54"/>
+      <c r="D81" s="54"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -11488,9 +11830,11 @@
       <c r="L81" s="3"/>
       <c r="M81" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N81" s="4" t="str">
         <f>IF(M81="","",IF(ISNUMBER(M81),IF(M81&lt;'Scoring Methodology'!$F$16,"Low",IF(M81&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M81&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
@@ -11501,21 +11845,23 @@
       <c r="U81" s="3"/>
       <c r="V81" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W81" s="4" t="str">
         <f>IF(V81="","",IF(ISNUMBER(V81),IF(V81&lt;'Scoring Methodology'!$F$16,"Low",IF(V81&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V81&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X81" s="3"/>
-      <c r="Y81" s="4" t="n">
+      <c r="Y81" s="4">
         <f>IF(E81="",0,IF(AND(OR(Dashboard!$L$7="All",Q81=Dashboard!$L$7),OR(Dashboard!$T$7="All",N81=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A82" s="18"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
+      <c r="A82" s="54"/>
+      <c r="B82" s="54"/>
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -11526,9 +11872,11 @@
       <c r="L82" s="3"/>
       <c r="M82" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N82" s="4" t="str">
         <f>IF(M82="","",IF(ISNUMBER(M82),IF(M82&lt;'Scoring Methodology'!$F$16,"Low",IF(M82&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M82&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
@@ -11539,21 +11887,23 @@
       <c r="U82" s="3"/>
       <c r="V82" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W82" s="4" t="str">
         <f>IF(V82="","",IF(ISNUMBER(V82),IF(V82&lt;'Scoring Methodology'!$F$16,"Low",IF(V82&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V82&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X82" s="3"/>
-      <c r="Y82" s="4" t="n">
+      <c r="Y82" s="4">
         <f>IF(E82="",0,IF(AND(OR(Dashboard!$L$7="All",Q82=Dashboard!$L$7),OR(Dashboard!$T$7="All",N82=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A83" s="18"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
+      <c r="A83" s="54"/>
+      <c r="B83" s="54"/>
+      <c r="C83" s="54"/>
+      <c r="D83" s="54"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -11564,9 +11914,11 @@
       <c r="L83" s="3"/>
       <c r="M83" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N83" s="4" t="str">
         <f>IF(M83="","",IF(ISNUMBER(M83),IF(M83&lt;'Scoring Methodology'!$F$16,"Low",IF(M83&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M83&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
@@ -11577,21 +11929,23 @@
       <c r="U83" s="3"/>
       <c r="V83" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W83" s="4" t="str">
         <f>IF(V83="","",IF(ISNUMBER(V83),IF(V83&lt;'Scoring Methodology'!$F$16,"Low",IF(V83&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V83&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X83" s="3"/>
-      <c r="Y83" s="4" t="n">
+      <c r="Y83" s="4">
         <f>IF(E83="",0,IF(AND(OR(Dashboard!$L$7="All",Q83=Dashboard!$L$7),OR(Dashboard!$T$7="All",N83=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A84" s="18"/>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="18"/>
+      <c r="A84" s="54"/>
+      <c r="B84" s="54"/>
+      <c r="C84" s="54"/>
+      <c r="D84" s="54"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -11602,9 +11956,11 @@
       <c r="L84" s="3"/>
       <c r="M84" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N84" s="4" t="str">
         <f>IF(M84="","",IF(ISNUMBER(M84),IF(M84&lt;'Scoring Methodology'!$F$16,"Low",IF(M84&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M84&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
@@ -11615,21 +11971,23 @@
       <c r="U84" s="3"/>
       <c r="V84" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W84" s="4" t="str">
         <f>IF(V84="","",IF(ISNUMBER(V84),IF(V84&lt;'Scoring Methodology'!$F$16,"Low",IF(V84&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V84&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X84" s="3"/>
-      <c r="Y84" s="4" t="n">
+      <c r="Y84" s="4">
         <f>IF(E84="",0,IF(AND(OR(Dashboard!$L$7="All",Q84=Dashboard!$L$7),OR(Dashboard!$T$7="All",N84=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A85" s="18"/>
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
+      <c r="A85" s="54"/>
+      <c r="B85" s="54"/>
+      <c r="C85" s="54"/>
+      <c r="D85" s="54"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
@@ -11640,9 +11998,11 @@
       <c r="L85" s="3"/>
       <c r="M85" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N85" s="4" t="str">
         <f>IF(M85="","",IF(ISNUMBER(M85),IF(M85&lt;'Scoring Methodology'!$F$16,"Low",IF(M85&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M85&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
@@ -11653,21 +12013,23 @@
       <c r="U85" s="3"/>
       <c r="V85" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W85" s="4" t="str">
         <f>IF(V85="","",IF(ISNUMBER(V85),IF(V85&lt;'Scoring Methodology'!$F$16,"Low",IF(V85&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V85&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X85" s="3"/>
-      <c r="Y85" s="4" t="n">
+      <c r="Y85" s="4">
         <f>IF(E85="",0,IF(AND(OR(Dashboard!$L$7="All",Q85=Dashboard!$L$7),OR(Dashboard!$T$7="All",N85=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A86" s="18"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
+      <c r="A86" s="54"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="54"/>
+      <c r="D86" s="54"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -11678,9 +12040,11 @@
       <c r="L86" s="3"/>
       <c r="M86" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N86" s="4" t="str">
         <f>IF(M86="","",IF(ISNUMBER(M86),IF(M86&lt;'Scoring Methodology'!$F$16,"Low",IF(M86&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M86&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
@@ -11691,21 +12055,23 @@
       <c r="U86" s="3"/>
       <c r="V86" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W86" s="4" t="str">
         <f>IF(V86="","",IF(ISNUMBER(V86),IF(V86&lt;'Scoring Methodology'!$F$16,"Low",IF(V86&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V86&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X86" s="3"/>
-      <c r="Y86" s="4" t="n">
+      <c r="Y86" s="4">
         <f>IF(E86="",0,IF(AND(OR(Dashboard!$L$7="All",Q86=Dashboard!$L$7),OR(Dashboard!$T$7="All",N86=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A87" s="18"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
+      <c r="A87" s="54"/>
+      <c r="B87" s="54"/>
+      <c r="C87" s="54"/>
+      <c r="D87" s="54"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -11716,9 +12082,11 @@
       <c r="L87" s="3"/>
       <c r="M87" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N87" s="4" t="str">
         <f>IF(M87="","",IF(ISNUMBER(M87),IF(M87&lt;'Scoring Methodology'!$F$16,"Low",IF(M87&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M87&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
@@ -11729,21 +12097,23 @@
       <c r="U87" s="3"/>
       <c r="V87" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W87" s="4" t="str">
         <f>IF(V87="","",IF(ISNUMBER(V87),IF(V87&lt;'Scoring Methodology'!$F$16,"Low",IF(V87&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V87&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X87" s="3"/>
-      <c r="Y87" s="4" t="n">
+      <c r="Y87" s="4">
         <f>IF(E87="",0,IF(AND(OR(Dashboard!$L$7="All",Q87=Dashboard!$L$7),OR(Dashboard!$T$7="All",N87=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A88" s="18"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
+      <c r="A88" s="54"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="54"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
@@ -11754,9 +12124,11 @@
       <c r="L88" s="3"/>
       <c r="M88" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N88" s="4" t="str">
         <f>IF(M88="","",IF(ISNUMBER(M88),IF(M88&lt;'Scoring Methodology'!$F$16,"Low",IF(M88&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M88&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
@@ -11767,21 +12139,23 @@
       <c r="U88" s="3"/>
       <c r="V88" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W88" s="4" t="str">
         <f>IF(V88="","",IF(ISNUMBER(V88),IF(V88&lt;'Scoring Methodology'!$F$16,"Low",IF(V88&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V88&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X88" s="3"/>
-      <c r="Y88" s="4" t="n">
+      <c r="Y88" s="4">
         <f>IF(E88="",0,IF(AND(OR(Dashboard!$L$7="All",Q88=Dashboard!$L$7),OR(Dashboard!$T$7="All",N88=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A89" s="18"/>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
+      <c r="A89" s="54"/>
+      <c r="B89" s="54"/>
+      <c r="C89" s="54"/>
+      <c r="D89" s="54"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -11792,9 +12166,11 @@
       <c r="L89" s="3"/>
       <c r="M89" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N89" s="4" t="str">
         <f>IF(M89="","",IF(ISNUMBER(M89),IF(M89&lt;'Scoring Methodology'!$F$16,"Low",IF(M89&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M89&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
@@ -11805,21 +12181,23 @@
       <c r="U89" s="3"/>
       <c r="V89" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W89" s="4" t="str">
         <f>IF(V89="","",IF(ISNUMBER(V89),IF(V89&lt;'Scoring Methodology'!$F$16,"Low",IF(V89&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V89&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X89" s="3"/>
-      <c r="Y89" s="4" t="n">
+      <c r="Y89" s="4">
         <f>IF(E89="",0,IF(AND(OR(Dashboard!$L$7="All",Q89=Dashboard!$L$7),OR(Dashboard!$T$7="All",N89=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A90" s="18"/>
-      <c r="B90" s="18"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18"/>
+      <c r="A90" s="54"/>
+      <c r="B90" s="54"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
@@ -11830,9 +12208,11 @@
       <c r="L90" s="3"/>
       <c r="M90" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N90" s="4" t="str">
         <f>IF(M90="","",IF(ISNUMBER(M90),IF(M90&lt;'Scoring Methodology'!$F$16,"Low",IF(M90&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M90&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
@@ -11843,21 +12223,23 @@
       <c r="U90" s="3"/>
       <c r="V90" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W90" s="4" t="str">
         <f>IF(V90="","",IF(ISNUMBER(V90),IF(V90&lt;'Scoring Methodology'!$F$16,"Low",IF(V90&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V90&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X90" s="3"/>
-      <c r="Y90" s="4" t="n">
+      <c r="Y90" s="4">
         <f>IF(E90="",0,IF(AND(OR(Dashboard!$L$7="All",Q90=Dashboard!$L$7),OR(Dashboard!$T$7="All",N90=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A91" s="18"/>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
+      <c r="A91" s="54"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="54"/>
+      <c r="D91" s="54"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
@@ -11868,9 +12250,11 @@
       <c r="L91" s="3"/>
       <c r="M91" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N91" s="4" t="str">
         <f>IF(M91="","",IF(ISNUMBER(M91),IF(M91&lt;'Scoring Methodology'!$F$16,"Low",IF(M91&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M91&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
@@ -11881,21 +12265,23 @@
       <c r="U91" s="3"/>
       <c r="V91" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W91" s="4" t="str">
         <f>IF(V91="","",IF(ISNUMBER(V91),IF(V91&lt;'Scoring Methodology'!$F$16,"Low",IF(V91&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V91&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X91" s="3"/>
-      <c r="Y91" s="4" t="n">
+      <c r="Y91" s="4">
         <f>IF(E91="",0,IF(AND(OR(Dashboard!$L$7="All",Q91=Dashboard!$L$7),OR(Dashboard!$T$7="All",N91=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A92" s="18"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
+      <c r="A92" s="54"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="54"/>
+      <c r="D92" s="54"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
@@ -11906,9 +12292,11 @@
       <c r="L92" s="3"/>
       <c r="M92" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N92" s="4" t="str">
         <f>IF(M92="","",IF(ISNUMBER(M92),IF(M92&lt;'Scoring Methodology'!$F$16,"Low",IF(M92&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M92&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -11919,21 +12307,23 @@
       <c r="U92" s="3"/>
       <c r="V92" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W92" s="4" t="str">
         <f>IF(V92="","",IF(ISNUMBER(V92),IF(V92&lt;'Scoring Methodology'!$F$16,"Low",IF(V92&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V92&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X92" s="3"/>
-      <c r="Y92" s="4" t="n">
+      <c r="Y92" s="4">
         <f>IF(E92="",0,IF(AND(OR(Dashboard!$L$7="All",Q92=Dashboard!$L$7),OR(Dashboard!$T$7="All",N92=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A93" s="18"/>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
+      <c r="A93" s="54"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
@@ -11944,9 +12334,11 @@
       <c r="L93" s="3"/>
       <c r="M93" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N93" s="4" t="str">
         <f>IF(M93="","",IF(ISNUMBER(M93),IF(M93&lt;'Scoring Methodology'!$F$16,"Low",IF(M93&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M93&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
@@ -11957,21 +12349,23 @@
       <c r="U93" s="3"/>
       <c r="V93" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W93" s="4" t="str">
         <f>IF(V93="","",IF(ISNUMBER(V93),IF(V93&lt;'Scoring Methodology'!$F$16,"Low",IF(V93&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V93&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X93" s="3"/>
-      <c r="Y93" s="4" t="n">
+      <c r="Y93" s="4">
         <f>IF(E93="",0,IF(AND(OR(Dashboard!$L$7="All",Q93=Dashboard!$L$7),OR(Dashboard!$T$7="All",N93=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A94" s="18"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="18"/>
+      <c r="A94" s="54"/>
+      <c r="B94" s="54"/>
+      <c r="C94" s="54"/>
+      <c r="D94" s="54"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
@@ -11982,9 +12376,11 @@
       <c r="L94" s="3"/>
       <c r="M94" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N94" s="4" t="str">
         <f>IF(M94="","",IF(ISNUMBER(M94),IF(M94&lt;'Scoring Methodology'!$F$16,"Low",IF(M94&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M94&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
@@ -11995,21 +12391,23 @@
       <c r="U94" s="3"/>
       <c r="V94" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W94" s="4" t="str">
         <f>IF(V94="","",IF(ISNUMBER(V94),IF(V94&lt;'Scoring Methodology'!$F$16,"Low",IF(V94&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V94&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X94" s="3"/>
-      <c r="Y94" s="4" t="n">
+      <c r="Y94" s="4">
         <f>IF(E94="",0,IF(AND(OR(Dashboard!$L$7="All",Q94=Dashboard!$L$7),OR(Dashboard!$T$7="All",N94=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A95" s="18"/>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
+      <c r="A95" s="54"/>
+      <c r="B95" s="54"/>
+      <c r="C95" s="54"/>
+      <c r="D95" s="54"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -12020,9 +12418,11 @@
       <c r="L95" s="3"/>
       <c r="M95" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N95" s="4" t="str">
         <f>IF(M95="","",IF(ISNUMBER(M95),IF(M95&lt;'Scoring Methodology'!$F$16,"Low",IF(M95&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M95&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
@@ -12033,21 +12433,23 @@
       <c r="U95" s="3"/>
       <c r="V95" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W95" s="4" t="str">
         <f>IF(V95="","",IF(ISNUMBER(V95),IF(V95&lt;'Scoring Methodology'!$F$16,"Low",IF(V95&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V95&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X95" s="3"/>
-      <c r="Y95" s="4" t="n">
+      <c r="Y95" s="4">
         <f>IF(E95="",0,IF(AND(OR(Dashboard!$L$7="All",Q95=Dashboard!$L$7),OR(Dashboard!$T$7="All",N95=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A96" s="18"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="18"/>
+      <c r="A96" s="54"/>
+      <c r="B96" s="54"/>
+      <c r="C96" s="54"/>
+      <c r="D96" s="54"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -12058,9 +12460,11 @@
       <c r="L96" s="3"/>
       <c r="M96" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N96" s="4" t="str">
         <f>IF(M96="","",IF(ISNUMBER(M96),IF(M96&lt;'Scoring Methodology'!$F$16,"Low",IF(M96&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M96&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
@@ -12071,21 +12475,23 @@
       <c r="U96" s="3"/>
       <c r="V96" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W96" s="4" t="str">
         <f>IF(V96="","",IF(ISNUMBER(V96),IF(V96&lt;'Scoring Methodology'!$F$16,"Low",IF(V96&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V96&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X96" s="3"/>
-      <c r="Y96" s="4" t="n">
+      <c r="Y96" s="4">
         <f>IF(E96="",0,IF(AND(OR(Dashboard!$L$7="All",Q96=Dashboard!$L$7),OR(Dashboard!$T$7="All",N96=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A97" s="18"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
+      <c r="A97" s="54"/>
+      <c r="B97" s="54"/>
+      <c r="C97" s="54"/>
+      <c r="D97" s="54"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -12096,9 +12502,11 @@
       <c r="L97" s="3"/>
       <c r="M97" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N97" s="4" t="str">
         <f>IF(M97="","",IF(ISNUMBER(M97),IF(M97&lt;'Scoring Methodology'!$F$16,"Low",IF(M97&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M97&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
@@ -12109,21 +12517,23 @@
       <c r="U97" s="3"/>
       <c r="V97" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W97" s="4" t="str">
         <f>IF(V97="","",IF(ISNUMBER(V97),IF(V97&lt;'Scoring Methodology'!$F$16,"Low",IF(V97&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V97&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X97" s="3"/>
-      <c r="Y97" s="4" t="n">
+      <c r="Y97" s="4">
         <f>IF(E97="",0,IF(AND(OR(Dashboard!$L$7="All",Q97=Dashboard!$L$7),OR(Dashboard!$T$7="All",N97=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A98" s="18"/>
-      <c r="B98" s="18"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
+      <c r="A98" s="54"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -12134,9 +12544,11 @@
       <c r="L98" s="3"/>
       <c r="M98" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N98" s="4" t="str">
         <f>IF(M98="","",IF(ISNUMBER(M98),IF(M98&lt;'Scoring Methodology'!$F$16,"Low",IF(M98&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M98&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
@@ -12147,21 +12559,23 @@
       <c r="U98" s="3"/>
       <c r="V98" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W98" s="4" t="str">
         <f>IF(V98="","",IF(ISNUMBER(V98),IF(V98&lt;'Scoring Methodology'!$F$16,"Low",IF(V98&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V98&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X98" s="3"/>
-      <c r="Y98" s="4" t="n">
+      <c r="Y98" s="4">
         <f>IF(E98="",0,IF(AND(OR(Dashboard!$L$7="All",Q98=Dashboard!$L$7),OR(Dashboard!$T$7="All",N98=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A99" s="18"/>
-      <c r="B99" s="18"/>
-      <c r="C99" s="18"/>
-      <c r="D99" s="18"/>
+      <c r="A99" s="54"/>
+      <c r="B99" s="54"/>
+      <c r="C99" s="54"/>
+      <c r="D99" s="54"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -12172,9 +12586,11 @@
       <c r="L99" s="3"/>
       <c r="M99" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N99" s="4" t="str">
         <f>IF(M99="","",IF(ISNUMBER(M99),IF(M99&lt;'Scoring Methodology'!$F$16,"Low",IF(M99&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M99&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
@@ -12185,21 +12601,23 @@
       <c r="U99" s="3"/>
       <c r="V99" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W99" s="4" t="str">
         <f>IF(V99="","",IF(ISNUMBER(V99),IF(V99&lt;'Scoring Methodology'!$F$16,"Low",IF(V99&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V99&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X99" s="3"/>
-      <c r="Y99" s="4" t="n">
+      <c r="Y99" s="4">
         <f>IF(E99="",0,IF(AND(OR(Dashboard!$L$7="All",Q99=Dashboard!$L$7),OR(Dashboard!$T$7="All",N99=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A100" s="18"/>
-      <c r="B100" s="18"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="18"/>
+      <c r="A100" s="54"/>
+      <c r="B100" s="54"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -12210,9 +12628,11 @@
       <c r="L100" s="3"/>
       <c r="M100" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N100" s="4" t="str">
         <f>IF(M100="","",IF(ISNUMBER(M100),IF(M100&lt;'Scoring Methodology'!$F$16,"Low",IF(M100&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M100&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
@@ -12223,21 +12643,23 @@
       <c r="U100" s="3"/>
       <c r="V100" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W100" s="4" t="str">
         <f>IF(V100="","",IF(ISNUMBER(V100),IF(V100&lt;'Scoring Methodology'!$F$16,"Low",IF(V100&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V100&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X100" s="3"/>
-      <c r="Y100" s="4" t="n">
+      <c r="Y100" s="4">
         <f>IF(E100="",0,IF(AND(OR(Dashboard!$L$7="All",Q100=Dashboard!$L$7),OR(Dashboard!$T$7="All",N100=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A101" s="18"/>
-      <c r="B101" s="18"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="18"/>
+      <c r="A101" s="54"/>
+      <c r="B101" s="54"/>
+      <c r="C101" s="54"/>
+      <c r="D101" s="54"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -12248,9 +12670,11 @@
       <c r="L101" s="3"/>
       <c r="M101" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N101" s="4" t="str">
         <f>IF(M101="","",IF(ISNUMBER(M101),IF(M101&lt;'Scoring Methodology'!$F$16,"Low",IF(M101&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M101&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
@@ -12261,21 +12685,23 @@
       <c r="U101" s="3"/>
       <c r="V101" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W101" s="4" t="str">
         <f>IF(V101="","",IF(ISNUMBER(V101),IF(V101&lt;'Scoring Methodology'!$F$16,"Low",IF(V101&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V101&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X101" s="3"/>
-      <c r="Y101" s="4" t="n">
+      <c r="Y101" s="4">
         <f>IF(E101="",0,IF(AND(OR(Dashboard!$L$7="All",Q101=Dashboard!$L$7),OR(Dashboard!$T$7="All",N101=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A102" s="18"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
+      <c r="A102" s="54"/>
+      <c r="B102" s="54"/>
+      <c r="C102" s="54"/>
+      <c r="D102" s="54"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -12286,9 +12712,11 @@
       <c r="L102" s="3"/>
       <c r="M102" s="4" t="str">
         <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="N102" s="4" t="str">
         <f>IF(M102="","",IF(ISNUMBER(M102),IF(M102&lt;'Scoring Methodology'!$F$16,"Low",IF(M102&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M102&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
@@ -12299,21 +12727,23 @@
       <c r="U102" s="3"/>
       <c r="V102" s="4" t="str">
         <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="W102" s="4" t="str">
         <f>IF(V102="","",IF(ISNUMBER(V102),IF(V102&lt;'Scoring Methodology'!$F$16,"Low",IF(V102&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V102&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X102" s="3"/>
-      <c r="Y102" s="4" t="n">
+      <c r="Y102" s="4">
         <f>IF(E102="",0,IF(AND(OR(Dashboard!$L$7="All",Q102=Dashboard!$L$7),OR(Dashboard!$T$7="All",N102=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A103" s="18"/>
-      <c r="B103" s="18"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="18"/>
+      <c r="A103" s="54"/>
+      <c r="B103" s="54"/>
+      <c r="C103" s="54"/>
+      <c r="D103" s="54"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
@@ -12324,9 +12754,11 @@
       <c r="L103" s="3"/>
       <c r="M103" s="4" t="str">
         <f t="shared" ref="M103:M106" si="6">IF(E103="","",IF(OR(K103="",L103=""),"",IF(AND(ISNUMBER(K103),ISNUMBER(L103),K103&gt;=1,K103&lt;=5,L103&gt;=1,L103&lt;=5,MOD(K103,1)=0,MOD(L103,1)=0),K103*L103,"Invalid input")))</f>
+        <v/>
       </c>
       <c r="N103" s="4" t="str">
         <f>IF(M103="","",IF(ISNUMBER(M103),IF(M103&lt;'Scoring Methodology'!$F$16,"Low",IF(M103&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M103&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
@@ -12337,21 +12769,23 @@
       <c r="U103" s="3"/>
       <c r="V103" s="4" t="str">
         <f t="shared" ref="V103:V106" si="7">IF(E103="","",IF(OR(T103="",U103=""),"",IF(AND(ISNUMBER(T103),ISNUMBER(U103),T103&gt;=1,T103&lt;=5,U103&gt;=1,U103&lt;=5,MOD(T103,1)=0,MOD(U103,1)=0),T103*U103,"Invalid input")))</f>
+        <v/>
       </c>
       <c r="W103" s="4" t="str">
         <f>IF(V103="","",IF(ISNUMBER(V103),IF(V103&lt;'Scoring Methodology'!$F$16,"Low",IF(V103&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V103&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X103" s="3"/>
-      <c r="Y103" s="4" t="n">
+      <c r="Y103" s="4">
         <f>IF(E103="",0,IF(AND(OR(Dashboard!$L$7="All",Q103=Dashboard!$L$7),OR(Dashboard!$T$7="All",N103=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A104" s="18"/>
-      <c r="B104" s="18"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="18"/>
+      <c r="A104" s="54"/>
+      <c r="B104" s="54"/>
+      <c r="C104" s="54"/>
+      <c r="D104" s="54"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
@@ -12362,9 +12796,11 @@
       <c r="L104" s="3"/>
       <c r="M104" s="4" t="str">
         <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="N104" s="4" t="str">
         <f>IF(M104="","",IF(ISNUMBER(M104),IF(M104&lt;'Scoring Methodology'!$F$16,"Low",IF(M104&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M104&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
@@ -12375,21 +12811,23 @@
       <c r="U104" s="3"/>
       <c r="V104" s="4" t="str">
         <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="W104" s="4" t="str">
         <f>IF(V104="","",IF(ISNUMBER(V104),IF(V104&lt;'Scoring Methodology'!$F$16,"Low",IF(V104&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V104&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X104" s="3"/>
-      <c r="Y104" s="4" t="n">
+      <c r="Y104" s="4">
         <f>IF(E104="",0,IF(AND(OR(Dashboard!$L$7="All",Q104=Dashboard!$L$7),OR(Dashboard!$T$7="All",N104=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A105" s="18"/>
-      <c r="B105" s="18"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="18"/>
+      <c r="A105" s="54"/>
+      <c r="B105" s="54"/>
+      <c r="C105" s="54"/>
+      <c r="D105" s="54"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
@@ -12400,9 +12838,11 @@
       <c r="L105" s="3"/>
       <c r="M105" s="4" t="str">
         <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="N105" s="4" t="str">
         <f>IF(M105="","",IF(ISNUMBER(M105),IF(M105&lt;'Scoring Methodology'!$F$16,"Low",IF(M105&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M105&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
@@ -12413,21 +12853,23 @@
       <c r="U105" s="3"/>
       <c r="V105" s="4" t="str">
         <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="W105" s="4" t="str">
         <f>IF(V105="","",IF(ISNUMBER(V105),IF(V105&lt;'Scoring Methodology'!$F$16,"Low",IF(V105&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V105&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X105" s="3"/>
-      <c r="Y105" s="4" t="n">
+      <c r="Y105" s="4">
         <f>IF(E105="",0,IF(AND(OR(Dashboard!$L$7="All",Q105=Dashboard!$L$7),OR(Dashboard!$T$7="All",N105=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:25" ht="26.1" customHeight="1">
-      <c r="A106" s="18"/>
-      <c r="B106" s="18"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="18"/>
+      <c r="A106" s="54"/>
+      <c r="B106" s="54"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="54"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
@@ -12438,9 +12880,11 @@
       <c r="L106" s="3"/>
       <c r="M106" s="4" t="str">
         <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="N106" s="4" t="str">
         <f>IF(M106="","",IF(ISNUMBER(M106),IF(M106&lt;'Scoring Methodology'!$F$16,"Low",IF(M106&lt;'Scoring Methodology'!$F$17,"Moderate",IF(M106&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
@@ -12451,39 +12895,41 @@
       <c r="U106" s="3"/>
       <c r="V106" s="4" t="str">
         <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="W106" s="4" t="str">
         <f>IF(V106="","",IF(ISNUMBER(V106),IF(V106&lt;'Scoring Methodology'!$F$16,"Low",IF(V106&lt;'Scoring Methodology'!$F$17,"Moderate",IF(V106&lt;'Scoring Methodology'!$F$18,"High","Critical"))),"Invalid input"))</f>
+        <v/>
       </c>
       <c r="X106" s="3"/>
-      <c r="Y106" s="4" t="n">
+      <c r="Y106" s="4">
         <f>IF(E106="",0,IF(AND(OR(Dashboard!$L$7="All",Q106=Dashboard!$L$7),OR(Dashboard!$T$7="All",N106=Dashboard!$T$7)),1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:25">
-      <c r="A107" s="18"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="18"/>
-      <c r="D107" s="18"/>
+      <c r="A107" s="54"/>
+      <c r="B107" s="54"/>
+      <c r="C107" s="54"/>
+      <c r="D107" s="54"/>
     </row>
     <row r="108" spans="1:25">
-      <c r="A108" s="18"/>
-      <c r="B108" s="18"/>
-      <c r="C108" s="18"/>
-      <c r="D108" s="18"/>
+      <c r="A108" s="54"/>
+      <c r="B108" s="54"/>
+      <c r="C108" s="54"/>
+      <c r="D108" s="54"/>
     </row>
     <row r="109" spans="1:25">
-      <c r="A109" s="18"/>
-      <c r="B109" s="18"/>
-      <c r="C109" s="18"/>
-      <c r="D109" s="18"/>
+      <c r="A109" s="54"/>
+      <c r="B109" s="54"/>
+      <c r="C109" s="54"/>
+      <c r="D109" s="54"/>
     </row>
     <row r="110" spans="1:25">
-      <c r="A110" s="18"/>
-      <c r="B110" s="18"/>
-      <c r="C110" s="18"/>
-      <c r="D110" s="18"/>
+      <c r="A110" s="54"/>
+      <c r="B110" s="54"/>
+      <c r="C110" s="54"/>
+      <c r="D110" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12656,20 +13102,20 @@
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
+      <c r="E5" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
     </row>
     <row r="6" spans="1:16" ht="45.95" customHeight="1">
       <c r="A6" s="18"/>
@@ -12677,40 +13123,40 @@
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="117.95" customHeight="1">
@@ -12719,34 +13165,34 @@
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K7" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="5"/>
       <c r="O7" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="26.1" customHeight="1">
@@ -12755,7 +13201,9 @@
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -14559,6 +15007,7 @@
   <mergeCells count="1">
     <mergeCell ref="E5:P5"/>
   </mergeCells>
+  <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="E7:E106">
     <cfRule type="expression" dxfId="15" priority="1">
       <formula>AND(E7&lt;&gt;"",COUNTIFS($E$7:$E$106,E7)&gt;1)</formula>
@@ -14716,22 +15165,22 @@
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
+      <c r="E5" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
     </row>
     <row r="6" spans="1:18" ht="45.95" customHeight="1">
       <c r="A6" s="18"/>
@@ -14739,46 +15188,46 @@
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="117.95" customHeight="1">
@@ -14787,34 +15236,34 @@
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="26.1" customHeight="1">
@@ -14823,7 +15272,9 @@
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -16825,6 +17276,7 @@
   <mergeCells count="1">
     <mergeCell ref="E5:R5"/>
   </mergeCells>
+  <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="E7:E106">
     <cfRule type="expression" dxfId="7" priority="1">
       <formula>AND(E7&lt;&gt;"",COUNTIFS($E$7:$E$106,E7)&gt;1)</formula>
@@ -16962,20 +17414,20 @@
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
+      <c r="E5" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
     </row>
     <row r="6" spans="1:16" ht="45.95" customHeight="1">
       <c r="A6" s="18"/>
@@ -16983,40 +17435,40 @@
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="117.95" customHeight="1">
@@ -17025,34 +17477,35 @@
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O7" s="4" t="str">
         <f t="shared" ref="O7:O38" ca="1" si="0">IF(E7="","",IF(ISNUMBER(K7),IF(J7="Completed",0,MAX(0,TODAY()-K7)),""))</f>
+        <v/>
       </c>
       <c r="P7" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="26.1" customHeight="1">
@@ -17061,7 +17514,9 @@
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -17072,6 +17527,7 @@
       <c r="N8" s="3"/>
       <c r="O8" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P8" s="3"/>
     </row>
@@ -17092,6 +17548,7 @@
       <c r="N9" s="3"/>
       <c r="O9" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P9" s="3"/>
     </row>
@@ -17112,6 +17569,7 @@
       <c r="N10" s="3"/>
       <c r="O10" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P10" s="3"/>
     </row>
@@ -17132,6 +17590,7 @@
       <c r="N11" s="3"/>
       <c r="O11" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P11" s="3"/>
     </row>
@@ -17152,6 +17611,7 @@
       <c r="N12" s="3"/>
       <c r="O12" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P12" s="3"/>
     </row>
@@ -17172,6 +17632,7 @@
       <c r="N13" s="3"/>
       <c r="O13" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P13" s="3"/>
     </row>
@@ -17192,6 +17653,7 @@
       <c r="N14" s="3"/>
       <c r="O14" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P14" s="3"/>
     </row>
@@ -17212,6 +17674,7 @@
       <c r="N15" s="3"/>
       <c r="O15" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P15" s="3"/>
     </row>
@@ -17232,6 +17695,7 @@
       <c r="N16" s="3"/>
       <c r="O16" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P16" s="3"/>
     </row>
@@ -17252,6 +17716,7 @@
       <c r="N17" s="3"/>
       <c r="O17" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P17" s="3"/>
     </row>
@@ -17272,6 +17737,7 @@
       <c r="N18" s="3"/>
       <c r="O18" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P18" s="3"/>
     </row>
@@ -17292,6 +17758,7 @@
       <c r="N19" s="3"/>
       <c r="O19" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P19" s="3"/>
     </row>
@@ -17312,6 +17779,7 @@
       <c r="N20" s="3"/>
       <c r="O20" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P20" s="3"/>
     </row>
@@ -17332,6 +17800,7 @@
       <c r="N21" s="3"/>
       <c r="O21" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P21" s="3"/>
     </row>
@@ -17352,6 +17821,7 @@
       <c r="N22" s="3"/>
       <c r="O22" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P22" s="3"/>
     </row>
@@ -17372,6 +17842,7 @@
       <c r="N23" s="3"/>
       <c r="O23" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P23" s="3"/>
     </row>
@@ -17392,6 +17863,7 @@
       <c r="N24" s="3"/>
       <c r="O24" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P24" s="3"/>
     </row>
@@ -17412,6 +17884,7 @@
       <c r="N25" s="3"/>
       <c r="O25" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P25" s="3"/>
     </row>
@@ -17432,6 +17905,7 @@
       <c r="N26" s="3"/>
       <c r="O26" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P26" s="3"/>
     </row>
@@ -17452,6 +17926,7 @@
       <c r="N27" s="3"/>
       <c r="O27" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P27" s="3"/>
     </row>
@@ -17472,6 +17947,7 @@
       <c r="N28" s="3"/>
       <c r="O28" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P28" s="3"/>
     </row>
@@ -17492,6 +17968,7 @@
       <c r="N29" s="3"/>
       <c r="O29" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P29" s="3"/>
     </row>
@@ -17512,6 +17989,7 @@
       <c r="N30" s="3"/>
       <c r="O30" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P30" s="3"/>
     </row>
@@ -17532,6 +18010,7 @@
       <c r="N31" s="3"/>
       <c r="O31" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P31" s="3"/>
     </row>
@@ -17552,6 +18031,7 @@
       <c r="N32" s="3"/>
       <c r="O32" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P32" s="3"/>
     </row>
@@ -17572,6 +18052,7 @@
       <c r="N33" s="3"/>
       <c r="O33" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P33" s="3"/>
     </row>
@@ -17592,6 +18073,7 @@
       <c r="N34" s="3"/>
       <c r="O34" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P34" s="3"/>
     </row>
@@ -17612,6 +18094,7 @@
       <c r="N35" s="3"/>
       <c r="O35" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P35" s="3"/>
     </row>
@@ -17632,6 +18115,7 @@
       <c r="N36" s="3"/>
       <c r="O36" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P36" s="3"/>
     </row>
@@ -17652,6 +18136,7 @@
       <c r="N37" s="3"/>
       <c r="O37" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P37" s="3"/>
     </row>
@@ -17672,6 +18157,7 @@
       <c r="N38" s="3"/>
       <c r="O38" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
+        <v/>
       </c>
       <c r="P38" s="3"/>
     </row>
@@ -17692,6 +18178,7 @@
       <c r="N39" s="3"/>
       <c r="O39" s="4" t="str">
         <f t="shared" ref="O39:O70" ca="1" si="1">IF(E39="","",IF(ISNUMBER(K39),IF(J39="Completed",0,MAX(0,TODAY()-K39)),""))</f>
+        <v/>
       </c>
       <c r="P39" s="3"/>
     </row>
@@ -17712,6 +18199,7 @@
       <c r="N40" s="3"/>
       <c r="O40" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P40" s="3"/>
     </row>
@@ -17732,6 +18220,7 @@
       <c r="N41" s="3"/>
       <c r="O41" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P41" s="3"/>
     </row>
@@ -17752,6 +18241,7 @@
       <c r="N42" s="3"/>
       <c r="O42" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P42" s="3"/>
     </row>
@@ -17772,6 +18262,7 @@
       <c r="N43" s="3"/>
       <c r="O43" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P43" s="3"/>
     </row>
@@ -17792,6 +18283,7 @@
       <c r="N44" s="3"/>
       <c r="O44" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P44" s="3"/>
     </row>
@@ -17812,6 +18304,7 @@
       <c r="N45" s="3"/>
       <c r="O45" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P45" s="3"/>
     </row>
@@ -17832,6 +18325,7 @@
       <c r="N46" s="3"/>
       <c r="O46" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P46" s="3"/>
     </row>
@@ -17852,6 +18346,7 @@
       <c r="N47" s="3"/>
       <c r="O47" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P47" s="3"/>
     </row>
@@ -17872,6 +18367,7 @@
       <c r="N48" s="3"/>
       <c r="O48" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P48" s="3"/>
     </row>
@@ -17892,6 +18388,7 @@
       <c r="N49" s="3"/>
       <c r="O49" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P49" s="3"/>
     </row>
@@ -17912,6 +18409,7 @@
       <c r="N50" s="3"/>
       <c r="O50" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P50" s="3"/>
     </row>
@@ -17932,6 +18430,7 @@
       <c r="N51" s="3"/>
       <c r="O51" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P51" s="3"/>
     </row>
@@ -17952,6 +18451,7 @@
       <c r="N52" s="3"/>
       <c r="O52" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P52" s="3"/>
     </row>
@@ -17972,6 +18472,7 @@
       <c r="N53" s="3"/>
       <c r="O53" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P53" s="3"/>
     </row>
@@ -17992,6 +18493,7 @@
       <c r="N54" s="3"/>
       <c r="O54" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P54" s="3"/>
     </row>
@@ -18012,6 +18514,7 @@
       <c r="N55" s="3"/>
       <c r="O55" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P55" s="3"/>
     </row>
@@ -18032,6 +18535,7 @@
       <c r="N56" s="3"/>
       <c r="O56" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P56" s="3"/>
     </row>
@@ -18052,6 +18556,7 @@
       <c r="N57" s="3"/>
       <c r="O57" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P57" s="3"/>
     </row>
@@ -18072,6 +18577,7 @@
       <c r="N58" s="3"/>
       <c r="O58" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P58" s="3"/>
     </row>
@@ -18092,6 +18598,7 @@
       <c r="N59" s="3"/>
       <c r="O59" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P59" s="3"/>
     </row>
@@ -18112,6 +18619,7 @@
       <c r="N60" s="3"/>
       <c r="O60" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P60" s="3"/>
     </row>
@@ -18132,6 +18640,7 @@
       <c r="N61" s="3"/>
       <c r="O61" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P61" s="3"/>
     </row>
@@ -18152,6 +18661,7 @@
       <c r="N62" s="3"/>
       <c r="O62" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P62" s="3"/>
     </row>
@@ -18172,6 +18682,7 @@
       <c r="N63" s="3"/>
       <c r="O63" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P63" s="3"/>
     </row>
@@ -18192,6 +18703,7 @@
       <c r="N64" s="3"/>
       <c r="O64" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P64" s="3"/>
     </row>
@@ -18212,6 +18724,7 @@
       <c r="N65" s="3"/>
       <c r="O65" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P65" s="3"/>
     </row>
@@ -18232,6 +18745,7 @@
       <c r="N66" s="3"/>
       <c r="O66" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P66" s="3"/>
     </row>
@@ -18252,6 +18766,7 @@
       <c r="N67" s="3"/>
       <c r="O67" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P67" s="3"/>
     </row>
@@ -18272,6 +18787,7 @@
       <c r="N68" s="3"/>
       <c r="O68" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P68" s="3"/>
     </row>
@@ -18292,6 +18808,7 @@
       <c r="N69" s="3"/>
       <c r="O69" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P69" s="3"/>
     </row>
@@ -18312,6 +18829,7 @@
       <c r="N70" s="3"/>
       <c r="O70" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
+        <v/>
       </c>
       <c r="P70" s="3"/>
     </row>
@@ -18332,6 +18850,7 @@
       <c r="N71" s="3"/>
       <c r="O71" s="4" t="str">
         <f t="shared" ref="O71:O106" ca="1" si="2">IF(E71="","",IF(ISNUMBER(K71),IF(J71="Completed",0,MAX(0,TODAY()-K71)),""))</f>
+        <v/>
       </c>
       <c r="P71" s="3"/>
     </row>
@@ -18352,6 +18871,7 @@
       <c r="N72" s="3"/>
       <c r="O72" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P72" s="3"/>
     </row>
@@ -18372,6 +18892,7 @@
       <c r="N73" s="3"/>
       <c r="O73" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P73" s="3"/>
     </row>
@@ -18392,6 +18913,7 @@
       <c r="N74" s="3"/>
       <c r="O74" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P74" s="3"/>
     </row>
@@ -18412,6 +18934,7 @@
       <c r="N75" s="3"/>
       <c r="O75" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P75" s="3"/>
     </row>
@@ -18432,6 +18955,7 @@
       <c r="N76" s="3"/>
       <c r="O76" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P76" s="3"/>
     </row>
@@ -18452,6 +18976,7 @@
       <c r="N77" s="3"/>
       <c r="O77" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P77" s="3"/>
     </row>
@@ -18472,6 +18997,7 @@
       <c r="N78" s="3"/>
       <c r="O78" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P78" s="3"/>
     </row>
@@ -18492,6 +19018,7 @@
       <c r="N79" s="3"/>
       <c r="O79" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P79" s="3"/>
     </row>
@@ -18512,6 +19039,7 @@
       <c r="N80" s="3"/>
       <c r="O80" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P80" s="3"/>
     </row>
@@ -18532,6 +19060,7 @@
       <c r="N81" s="3"/>
       <c r="O81" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P81" s="3"/>
     </row>
@@ -18552,6 +19081,7 @@
       <c r="N82" s="3"/>
       <c r="O82" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P82" s="3"/>
     </row>
@@ -18572,6 +19102,7 @@
       <c r="N83" s="3"/>
       <c r="O83" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P83" s="3"/>
     </row>
@@ -18592,6 +19123,7 @@
       <c r="N84" s="3"/>
       <c r="O84" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P84" s="3"/>
     </row>
@@ -18612,6 +19144,7 @@
       <c r="N85" s="3"/>
       <c r="O85" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P85" s="3"/>
     </row>
@@ -18632,6 +19165,7 @@
       <c r="N86" s="3"/>
       <c r="O86" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P86" s="3"/>
     </row>
@@ -18652,6 +19186,7 @@
       <c r="N87" s="3"/>
       <c r="O87" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P87" s="3"/>
     </row>
@@ -18672,6 +19207,7 @@
       <c r="N88" s="3"/>
       <c r="O88" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P88" s="3"/>
     </row>
@@ -18692,6 +19228,7 @@
       <c r="N89" s="3"/>
       <c r="O89" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P89" s="3"/>
     </row>
@@ -18712,6 +19249,7 @@
       <c r="N90" s="3"/>
       <c r="O90" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P90" s="3"/>
     </row>
@@ -18732,6 +19270,7 @@
       <c r="N91" s="3"/>
       <c r="O91" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P91" s="3"/>
     </row>
@@ -18752,6 +19291,7 @@
       <c r="N92" s="3"/>
       <c r="O92" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P92" s="3"/>
     </row>
@@ -18772,6 +19312,7 @@
       <c r="N93" s="3"/>
       <c r="O93" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P93" s="3"/>
     </row>
@@ -18792,6 +19333,7 @@
       <c r="N94" s="3"/>
       <c r="O94" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P94" s="3"/>
     </row>
@@ -18812,6 +19354,7 @@
       <c r="N95" s="3"/>
       <c r="O95" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P95" s="3"/>
     </row>
@@ -18832,6 +19375,7 @@
       <c r="N96" s="3"/>
       <c r="O96" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P96" s="3"/>
     </row>
@@ -18852,6 +19396,7 @@
       <c r="N97" s="3"/>
       <c r="O97" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P97" s="3"/>
     </row>
@@ -18872,6 +19417,7 @@
       <c r="N98" s="3"/>
       <c r="O98" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P98" s="3"/>
     </row>
@@ -18892,6 +19438,7 @@
       <c r="N99" s="3"/>
       <c r="O99" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P99" s="3"/>
     </row>
@@ -18912,6 +19459,7 @@
       <c r="N100" s="3"/>
       <c r="O100" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P100" s="3"/>
     </row>
@@ -18932,6 +19480,7 @@
       <c r="N101" s="3"/>
       <c r="O101" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P101" s="3"/>
     </row>
@@ -18952,6 +19501,7 @@
       <c r="N102" s="3"/>
       <c r="O102" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P102" s="3"/>
     </row>
@@ -18972,6 +19522,7 @@
       <c r="N103" s="3"/>
       <c r="O103" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P103" s="3"/>
     </row>
@@ -18992,6 +19543,7 @@
       <c r="N104" s="3"/>
       <c r="O104" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P104" s="3"/>
     </row>
@@ -19012,6 +19564,7 @@
       <c r="N105" s="3"/>
       <c r="O105" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P105" s="3"/>
     </row>
@@ -19032,6 +19585,7 @@
       <c r="N106" s="3"/>
       <c r="O106" s="4" t="str">
         <f t="shared" ca="1" si="2"/>
+        <v/>
       </c>
       <c r="P106" s="3"/>
     </row>
@@ -19063,6 +19617,7 @@
   <mergeCells count="1">
     <mergeCell ref="E5:P5"/>
   </mergeCells>
+  <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="E7:E106">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(E7&lt;&gt;"",COUNTIFS($E$7:$E$106,E7)&gt;1)</formula>
@@ -19202,58 +19757,58 @@
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
+      <c r="E5" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
     </row>
     <row r="6" spans="1:16" ht="26.1" customHeight="1">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
+      <c r="E6" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
     </row>
     <row r="7" spans="1:16" ht="26.1" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
     </row>
     <row r="8" spans="1:16" ht="26.1" customHeight="1">
       <c r="A8" s="18"/>
@@ -19261,16 +19816,16 @@
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
       <c r="E8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -19290,13 +19845,13 @@
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -19316,13 +19871,13 @@
         <v>2</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -19342,13 +19897,13 @@
         <v>3</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -19368,13 +19923,13 @@
         <v>4</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -19394,13 +19949,13 @@
         <v>5</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -19435,13 +19990,13 @@
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -19459,12 +20014,12 @@
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F16" s="1">
-        <v>5</v>
-      </c>
-      <c r="G16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="1"/>
@@ -19483,12 +20038,12 @@
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="F17" s="1">
         <v>12</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="1">
         <v>19</v>
       </c>
       <c r="H17" s="1"/>
@@ -19507,9 +20062,9 @@
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
       <c r="E18" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="F18" s="1">
         <v>20</v>
       </c>
       <c r="G18" s="1">
@@ -19531,13 +20086,13 @@
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -19590,56 +20145,56 @@
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="37" t="str">
-        <v>Scoring decision | October 14, 2026: Restored user-defined bands: Low 1–4, Moderate 5–11, High 12–19, Critical 20–25. Supersedes High 10–16 / Critical 17–25. Moderate covers 10–11 so the scale has no gaps. R-001: 3 × 4 = 12 High remains simulated and pending validation.</v>
-      </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
+      <c r="E22" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
     </row>
     <row r="23" spans="1:16" ht="26.1" customHeight="1">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
+      <c r="P23" s="48"/>
     </row>
     <row r="24" spans="1:16" ht="26.1" customHeight="1">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="37"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
     </row>
     <row r="25" spans="1:16" ht="26.1" customHeight="1">
       <c r="A25" s="18"/>
@@ -19664,74 +20219,74 @@
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="37"/>
+      <c r="E26" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
     </row>
     <row r="27" spans="1:16" ht="26.1" customHeight="1">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
     </row>
     <row r="28" spans="1:16" ht="26.1" customHeight="1">
       <c r="A28" s="18"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
     </row>
     <row r="29" spans="1:16" ht="26.1" customHeight="1">
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="37"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
     </row>
     <row r="30" spans="1:16" ht="26.1" customHeight="1">
       <c r="A30" s="18"/>
@@ -19756,74 +20311,74 @@
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
-      <c r="E31" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-      <c r="O31" s="37"/>
-      <c r="P31" s="37"/>
+      <c r="E31" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="48"/>
     </row>
     <row r="32" spans="1:16" ht="26.1" customHeight="1">
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="37"/>
-      <c r="P32" s="37"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
+      <c r="O32" s="48"/>
+      <c r="P32" s="48"/>
     </row>
     <row r="33" spans="1:16" ht="26.1" customHeight="1">
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="37"/>
-      <c r="N33" s="37"/>
-      <c r="O33" s="37"/>
-      <c r="P33" s="37"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
+      <c r="N33" s="48"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="48"/>
     </row>
     <row r="34" spans="1:16" ht="26.1" customHeight="1">
       <c r="A34" s="18"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37"/>
-      <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-      <c r="P34" s="37"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="48"/>
+      <c r="O34" s="48"/>
+      <c r="P34" s="48"/>
     </row>
     <row r="35" spans="1:16" ht="26.1" customHeight="1">
       <c r="A35" s="18"/>
@@ -20431,96 +20986,96 @@
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
+      <c r="E5" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
     </row>
     <row r="6" spans="1:16" ht="26.1" customHeight="1">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
+      <c r="E6" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
     </row>
     <row r="7" spans="1:16" ht="26.1" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
+      <c r="E7" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
     </row>
     <row r="8" spans="1:16" ht="26.1" customHeight="1">
       <c r="A8" s="18"/>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="52"/>
     </row>
     <row r="9" spans="1:16" ht="26.1" customHeight="1">
       <c r="A9" s="18"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
     </row>
     <row r="10" spans="1:16" ht="26.1" customHeight="1">
       <c r="A10" s="18"/>
@@ -20545,76 +21100,76 @@
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
-      <c r="E11" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
+      <c r="E11" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
     </row>
     <row r="12" spans="1:16" ht="26.1" customHeight="1">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
-      <c r="E12" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
+      <c r="E12" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
     </row>
     <row r="13" spans="1:16" ht="26.1" customHeight="1">
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
     </row>
     <row r="14" spans="1:16" ht="26.1" customHeight="1">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
     </row>
     <row r="15" spans="1:16" ht="26.1" customHeight="1">
       <c r="A15" s="18"/>
@@ -20639,76 +21194,76 @@
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
+      <c r="E16" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
     </row>
     <row r="17" spans="1:16" ht="26.1" customHeight="1">
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
+      <c r="E17" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
     </row>
     <row r="18" spans="1:16" ht="26.1" customHeight="1">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="52"/>
     </row>
     <row r="19" spans="1:16" ht="26.1" customHeight="1">
       <c r="A19" s="18"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="52"/>
+      <c r="P19" s="52"/>
     </row>
     <row r="20" spans="1:16" ht="26.1" customHeight="1">
       <c r="A20" s="18"/>
@@ -20733,76 +21288,76 @@
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
-      <c r="E21" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
+      <c r="E21" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51"/>
     </row>
     <row r="22" spans="1:16" ht="26.1" customHeight="1">
       <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
-      <c r="E22" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
+      <c r="E22" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="50"/>
     </row>
     <row r="23" spans="1:16" ht="26.1" customHeight="1">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="39"/>
-      <c r="P23" s="39"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="50"/>
     </row>
     <row r="24" spans="1:16" ht="26.1" customHeight="1">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="39"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
     </row>
     <row r="25" spans="1:16" ht="26.1" customHeight="1">
       <c r="A25" s="18"/>
@@ -20827,76 +21382,76 @@
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
-      <c r="E26" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="40"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="40"/>
+      <c r="E26" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="51"/>
+      <c r="P26" s="51"/>
     </row>
     <row r="27" spans="1:16" ht="26.1" customHeight="1">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
-      <c r="E27" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
+      <c r="E27" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
     </row>
     <row r="28" spans="1:16" ht="26.1" customHeight="1">
       <c r="A28" s="18"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
     </row>
     <row r="29" spans="1:16" ht="26.1" customHeight="1">
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="53"/>
     </row>
     <row r="30" spans="1:16" ht="26.1" customHeight="1">
       <c r="A30" s="18"/>
@@ -20921,76 +21476,76 @@
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
-      <c r="E31" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="40"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
+      <c r="E31" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="51"/>
     </row>
     <row r="32" spans="1:16" ht="26.1" customHeight="1">
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
-      <c r="E32" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="39"/>
-      <c r="M32" s="39"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="39"/>
-      <c r="P32" s="39"/>
+      <c r="E32" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="50"/>
     </row>
     <row r="33" spans="1:16" ht="26.1" customHeight="1">
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="39"/>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="39"/>
-      <c r="P33" s="39"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="50"/>
     </row>
     <row r="34" spans="1:16" ht="26.1" customHeight="1">
       <c r="A34" s="18"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="50"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="50"/>
+      <c r="P34" s="50"/>
     </row>
     <row r="35" spans="1:16" ht="26.1" customHeight="1">
       <c r="A35" s="18"/>
@@ -21015,76 +21570,76 @@
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
-      <c r="E36" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
+      <c r="E36" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="51"/>
+      <c r="P36" s="51"/>
     </row>
     <row r="37" spans="1:16" ht="26.1" customHeight="1">
       <c r="A37" s="18"/>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
-      <c r="E37" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
-      <c r="N37" s="41"/>
-      <c r="O37" s="41"/>
-      <c r="P37" s="41"/>
+      <c r="E37" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="52"/>
+      <c r="P37" s="52"/>
     </row>
     <row r="38" spans="1:16" ht="26.1" customHeight="1">
       <c r="A38" s="18"/>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="41"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
     </row>
     <row r="39" spans="1:16" ht="26.1" customHeight="1">
       <c r="A39" s="18"/>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="41"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
     </row>
     <row r="40" spans="1:16" ht="26.1" customHeight="1">
       <c r="A40" s="18"/>
@@ -21109,76 +21664,76 @@
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
-      <c r="E41" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="40"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
+      <c r="E41" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+      <c r="L41" s="51"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="51"/>
+      <c r="O41" s="51"/>
+      <c r="P41" s="51"/>
     </row>
     <row r="42" spans="1:16" ht="26.1" customHeight="1">
       <c r="A42" s="18"/>
       <c r="B42" s="18"/>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
-      <c r="E42" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="39"/>
-      <c r="L42" s="39"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="39"/>
+      <c r="E42" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="50"/>
+      <c r="L42" s="50"/>
+      <c r="M42" s="50"/>
+      <c r="N42" s="50"/>
+      <c r="O42" s="50"/>
+      <c r="P42" s="50"/>
     </row>
     <row r="43" spans="1:16" ht="26.1" customHeight="1">
       <c r="A43" s="18"/>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="39"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
+      <c r="P43" s="50"/>
     </row>
     <row r="44" spans="1:16" ht="26.1" customHeight="1">
       <c r="A44" s="18"/>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="39"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="50"/>
     </row>
     <row r="45" spans="1:16" ht="26.1" customHeight="1">
       <c r="A45" s="18"/>
